--- a/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
@@ -396,10 +396,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>16.12841067008485</v>
+        <v>16.13</v>
       </c>
       <c r="B2">
-        <v>0.5003424657534247</v>
+        <v>0.5</v>
       </c>
       <c r="C2">
         <v>730.5</v>
@@ -411,7 +411,7 @@
         <v>13.51</v>
       </c>
       <c r="F2">
-        <v>7.505</v>
+        <v>7.51</v>
       </c>
       <c r="G2">
         <v>23.02</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>15.98407914356262</v>
+        <v>15.98</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -481,7 +481,7 @@
         <v>13.01</v>
       </c>
       <c r="F2">
-        <v>7.505</v>
+        <v>7.51</v>
       </c>
       <c r="G2">
         <v>22.63</v>
@@ -544,13 +544,13 @@
         <v>523</v>
       </c>
       <c r="C2">
-        <v>1.893</v>
+        <v>1.89</v>
       </c>
       <c r="D2">
-        <v>2.548</v>
+        <v>2.55</v>
       </c>
       <c r="E2">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F2">
         <v>16.79</v>
@@ -575,7 +575,7 @@
         <v>6.64</v>
       </c>
       <c r="E3">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F3">
         <v>26.09</v>
@@ -594,16 +594,16 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>1.128</v>
+        <v>1.13</v>
       </c>
       <c r="D4">
-        <v>0.8203</v>
+        <v>0.82</v>
       </c>
       <c r="E4">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F4">
-        <v>2.502</v>
+        <v>2.5</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -619,16 +619,16 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>1.334</v>
+        <v>1.33</v>
       </c>
       <c r="D5">
-        <v>0.7533</v>
+        <v>0.75</v>
       </c>
       <c r="E5">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F5">
-        <v>2.502</v>
+        <v>2.5</v>
       </c>
       <c r="G5">
         <v>6</v>
@@ -644,13 +644,13 @@
         <v>397</v>
       </c>
       <c r="C6">
-        <v>1.348</v>
+        <v>1.35</v>
       </c>
       <c r="D6">
-        <v>1.734</v>
+        <v>1.73</v>
       </c>
       <c r="E6">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
         <v>10.98</v>
@@ -669,13 +669,13 @@
         <v>2917</v>
       </c>
       <c r="C7">
-        <v>2.762</v>
+        <v>2.76</v>
       </c>
       <c r="D7">
-        <v>5.586</v>
+        <v>5.59</v>
       </c>
       <c r="E7">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F7">
         <v>79.40000000000001</v>
@@ -694,13 +694,13 @@
         <v>3226</v>
       </c>
       <c r="C8">
-        <v>2.055</v>
+        <v>2.06</v>
       </c>
       <c r="D8">
-        <v>3.593</v>
+        <v>3.59</v>
       </c>
       <c r="E8">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
         <v>40.58</v>
@@ -722,10 +722,10 @@
         <v>1.77</v>
       </c>
       <c r="D9">
-        <v>4.132</v>
+        <v>4.13</v>
       </c>
       <c r="E9">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F9">
         <v>34.6</v>
@@ -744,13 +744,13 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="E10">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F10">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -766,16 +766,16 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>1.198</v>
+        <v>1.2</v>
       </c>
       <c r="D11">
-        <v>2.438</v>
+        <v>2.44</v>
       </c>
       <c r="E11">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
-        <v>3.949</v>
+        <v>3.95</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -791,16 +791,16 @@
         <v>45</v>
       </c>
       <c r="C12">
-        <v>1.193</v>
+        <v>1.19</v>
       </c>
       <c r="D12">
-        <v>1.734</v>
+        <v>1.73</v>
       </c>
       <c r="E12">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F12">
-        <v>8.569000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="G12">
         <v>21</v>
@@ -816,16 +816,16 @@
         <v>142</v>
       </c>
       <c r="C13">
-        <v>1.031</v>
+        <v>1.03</v>
       </c>
       <c r="D13">
-        <v>1.047</v>
+        <v>1.05</v>
       </c>
       <c r="E13">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F13">
-        <v>5.504</v>
+        <v>5.5</v>
       </c>
       <c r="G13">
         <v>74</v>
@@ -841,16 +841,16 @@
         <v>3</v>
       </c>
       <c r="C14">
-        <v>0.6657</v>
+        <v>0.67</v>
       </c>
       <c r="D14">
-        <v>0.8449</v>
+        <v>0.84</v>
       </c>
       <c r="E14">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F14">
-        <v>1.964</v>
+        <v>1.96</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -866,16 +866,16 @@
         <v>7</v>
       </c>
       <c r="C15">
-        <v>0.7005</v>
+        <v>0.7</v>
       </c>
       <c r="D15">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="E15">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -891,16 +891,16 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>0.6041</v>
+        <v>0.6</v>
       </c>
       <c r="D16">
-        <v>0.2004</v>
+        <v>0.2</v>
       </c>
       <c r="E16">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F16">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>6</v>
@@ -916,16 +916,16 @@
         <v>139</v>
       </c>
       <c r="C17">
-        <v>1.543</v>
+        <v>1.54</v>
       </c>
       <c r="D17">
         <v>1.12</v>
       </c>
       <c r="E17">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F17">
-        <v>5.003</v>
+        <v>5</v>
       </c>
       <c r="G17">
         <v>46</v>
@@ -941,16 +941,16 @@
         <v>2</v>
       </c>
       <c r="C18">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F18">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -966,16 +966,16 @@
         <v>19</v>
       </c>
       <c r="C19">
-        <v>1.901</v>
+        <v>1.9</v>
       </c>
       <c r="D19">
-        <v>2.105</v>
+        <v>2.11</v>
       </c>
       <c r="E19">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F19">
-        <v>5.504</v>
+        <v>5.5</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -991,13 +991,13 @@
         <v>143</v>
       </c>
       <c r="C20">
-        <v>1.646</v>
+        <v>1.65</v>
       </c>
       <c r="D20">
-        <v>2.113</v>
+        <v>2.11</v>
       </c>
       <c r="E20">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F20">
         <v>10.01</v>
@@ -1016,16 +1016,16 @@
         <v>21527</v>
       </c>
       <c r="C21">
-        <v>2.457</v>
+        <v>2.46</v>
       </c>
       <c r="D21">
         <v>5.31</v>
       </c>
       <c r="E21">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F21">
-        <v>162</v>
+        <v>162.05</v>
       </c>
       <c r="G21">
         <v>4812</v>
@@ -1041,16 +1041,16 @@
         <v>59323</v>
       </c>
       <c r="C22">
-        <v>2.763</v>
+        <v>2.76</v>
       </c>
       <c r="D22">
-        <v>5.351</v>
+        <v>5.35</v>
       </c>
       <c r="E22">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F22">
-        <v>186.4</v>
+        <v>186.45</v>
       </c>
       <c r="G22">
         <v>11772</v>
@@ -1066,13 +1066,13 @@
         <v>2474</v>
       </c>
       <c r="C23">
-        <v>2.621</v>
+        <v>2.62</v>
       </c>
       <c r="D23">
-        <v>5.868</v>
+        <v>5.87</v>
       </c>
       <c r="E23">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F23">
         <v>60.88</v>
@@ -1091,13 +1091,13 @@
         <v>178</v>
       </c>
       <c r="C24">
-        <v>2.586</v>
+        <v>2.59</v>
       </c>
       <c r="D24">
-        <v>3.346</v>
+        <v>3.35</v>
       </c>
       <c r="E24">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F24">
         <v>15.01</v>
@@ -1116,13 +1116,13 @@
         <v>248</v>
       </c>
       <c r="C25">
-        <v>3.346</v>
+        <v>3.35</v>
       </c>
       <c r="D25">
-        <v>8.451000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E25">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F25">
         <v>54.11</v>
@@ -1141,16 +1141,16 @@
         <v>110</v>
       </c>
       <c r="C26">
-        <v>0.7958</v>
+        <v>0.8</v>
       </c>
       <c r="D26">
-        <v>1.093</v>
+        <v>1.09</v>
       </c>
       <c r="E26">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F26">
-        <v>7.689</v>
+        <v>7.69</v>
       </c>
       <c r="G26">
         <v>76</v>
@@ -1166,13 +1166,13 @@
         <v>1</v>
       </c>
       <c r="C27">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="E27">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F27">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -1188,13 +1188,13 @@
         <v>1</v>
       </c>
       <c r="C28">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="E28">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F28">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1210,13 +1210,13 @@
         <v>2262</v>
       </c>
       <c r="C29">
-        <v>2.119</v>
+        <v>2.12</v>
       </c>
       <c r="D29">
-        <v>2.763</v>
+        <v>2.76</v>
       </c>
       <c r="E29">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F29">
         <v>19.51</v>
@@ -1235,13 +1235,13 @@
         <v>16737</v>
       </c>
       <c r="C30">
-        <v>1.677</v>
+        <v>1.68</v>
       </c>
       <c r="D30">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="E30">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F30">
         <v>146.1</v>
@@ -1266,10 +1266,10 @@
         <v>13.73</v>
       </c>
       <c r="E31">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F31">
-        <v>365.2</v>
+        <v>365.25</v>
       </c>
       <c r="G31">
         <v>23947</v>
@@ -1291,7 +1291,7 @@
         <v>14.9</v>
       </c>
       <c r="E32">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F32">
         <v>730.5</v>
@@ -1313,13 +1313,13 @@
         <v>1.93</v>
       </c>
       <c r="D33">
-        <v>2.258</v>
+        <v>2.26</v>
       </c>
       <c r="E33">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F33">
-        <v>6.012</v>
+        <v>6.01</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -1335,16 +1335,16 @@
         <v>7106</v>
       </c>
       <c r="C34">
-        <v>2.069</v>
+        <v>2.07</v>
       </c>
       <c r="D34">
-        <v>5.968</v>
+        <v>5.97</v>
       </c>
       <c r="E34">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F34">
-        <v>137</v>
+        <v>136.97</v>
       </c>
       <c r="G34">
         <v>1851</v>
@@ -1360,16 +1360,16 @@
         <v>93</v>
       </c>
       <c r="C35">
-        <v>1.089</v>
+        <v>1.09</v>
       </c>
       <c r="D35">
-        <v>1.505</v>
+        <v>1.5</v>
       </c>
       <c r="E35">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F35">
-        <v>8.909000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="G35">
         <v>47</v>
@@ -1385,13 +1385,13 @@
         <v>1352</v>
       </c>
       <c r="C36">
-        <v>1.891</v>
+        <v>1.89</v>
       </c>
       <c r="D36">
-        <v>3.217</v>
+        <v>3.22</v>
       </c>
       <c r="E36">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F36">
         <v>28.1</v>
@@ -1410,16 +1410,16 @@
         <v>7</v>
       </c>
       <c r="C37">
-        <v>0.5837</v>
+        <v>0.58</v>
       </c>
       <c r="D37">
-        <v>0.2043</v>
+        <v>0.2</v>
       </c>
       <c r="E37">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F37">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G37">
         <v>6</v>
@@ -1435,13 +1435,13 @@
         <v>221</v>
       </c>
       <c r="C38">
-        <v>2.895</v>
+        <v>2.89</v>
       </c>
       <c r="D38">
-        <v>6.115</v>
+        <v>6.12</v>
       </c>
       <c r="E38">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F38">
         <v>32.23</v>
@@ -1460,13 +1460,13 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -1485,10 +1485,10 @@
         <v>2</v>
       </c>
       <c r="D40">
-        <v>3.089</v>
+        <v>3.09</v>
       </c>
       <c r="E40">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F40">
         <v>34.02</v>
@@ -1507,16 +1507,16 @@
         <v>4</v>
       </c>
       <c r="C41">
-        <v>0.7428</v>
+        <v>0.74</v>
       </c>
       <c r="D41">
-        <v>0.543</v>
+        <v>0.54</v>
       </c>
       <c r="E41">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F41">
-        <v>1.441</v>
+        <v>1.44</v>
       </c>
       <c r="G41">
         <v>3</v>
@@ -1532,16 +1532,16 @@
         <v>3</v>
       </c>
       <c r="C42">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F42">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="G42">
         <v>3</v>
@@ -1557,13 +1557,13 @@
         <v>135</v>
       </c>
       <c r="C43">
-        <v>7.395</v>
+        <v>7.39</v>
       </c>
       <c r="D43">
         <v>20.24</v>
       </c>
       <c r="E43">
-        <v>3.502</v>
+        <v>3.5</v>
       </c>
       <c r="F43">
         <v>74.70999999999999</v>
@@ -1582,13 +1582,13 @@
         <v>484</v>
       </c>
       <c r="C44">
-        <v>1.934</v>
+        <v>1.93</v>
       </c>
       <c r="D44">
-        <v>2.949</v>
+        <v>2.95</v>
       </c>
       <c r="E44">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F44">
         <v>19.73</v>
@@ -1607,16 +1607,16 @@
         <v>5</v>
       </c>
       <c r="C45">
-        <v>2.624</v>
+        <v>2.62</v>
       </c>
       <c r="D45">
-        <v>0.2774</v>
+        <v>0.28</v>
       </c>
       <c r="E45">
-        <v>2.403</v>
+        <v>2.4</v>
       </c>
       <c r="F45">
-        <v>2.795</v>
+        <v>2.8</v>
       </c>
       <c r="G45">
         <v>2</v>
@@ -1635,10 +1635,10 @@
         <v>1.37</v>
       </c>
       <c r="D46">
-        <v>2.415</v>
+        <v>2.42</v>
       </c>
       <c r="E46">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F46">
         <v>20.29</v>
@@ -1657,16 +1657,16 @@
         <v>13</v>
       </c>
       <c r="C47">
-        <v>0.9892</v>
+        <v>0.99</v>
       </c>
       <c r="D47">
-        <v>1.156</v>
+        <v>1.16</v>
       </c>
       <c r="E47">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F47">
-        <v>3.176</v>
+        <v>3.18</v>
       </c>
       <c r="G47">
         <v>8</v>
@@ -1688,7 +1688,7 @@
         <v>2.23</v>
       </c>
       <c r="E48">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F48">
         <v>12.95</v>
@@ -1707,16 +1707,16 @@
         <v>5</v>
       </c>
       <c r="C49">
-        <v>0.7145</v>
+        <v>0.71</v>
       </c>
       <c r="D49">
-        <v>0.2881</v>
+        <v>0.29</v>
       </c>
       <c r="E49">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F49">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G49">
         <v>4</v>
@@ -1732,16 +1732,16 @@
         <v>792</v>
       </c>
       <c r="C50">
-        <v>1.528</v>
+        <v>1.53</v>
       </c>
       <c r="D50">
-        <v>1.508</v>
+        <v>1.51</v>
       </c>
       <c r="E50">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F50">
-        <v>8.506</v>
+        <v>8.51</v>
       </c>
       <c r="G50">
         <v>269</v>
@@ -1757,16 +1757,16 @@
         <v>23</v>
       </c>
       <c r="C51">
-        <v>0.8126</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D51">
-        <v>0.3531</v>
+        <v>0.35</v>
       </c>
       <c r="E51">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F51">
-        <v>1.501</v>
+        <v>1.5</v>
       </c>
       <c r="G51">
         <v>15</v>
@@ -1782,16 +1782,16 @@
         <v>59</v>
       </c>
       <c r="C52">
-        <v>0.9546</v>
+        <v>0.95</v>
       </c>
       <c r="D52">
-        <v>0.5603</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E52">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F52">
-        <v>2.502</v>
+        <v>2.5</v>
       </c>
       <c r="G52">
         <v>32</v>
@@ -1807,13 +1807,13 @@
         <v>374</v>
       </c>
       <c r="C53">
-        <v>1.631</v>
+        <v>1.63</v>
       </c>
       <c r="D53">
-        <v>2.024</v>
+        <v>2.02</v>
       </c>
       <c r="E53">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F53">
         <v>14.05</v>
@@ -1832,16 +1832,16 @@
         <v>5</v>
       </c>
       <c r="C54">
-        <v>0.7024</v>
+        <v>0.7</v>
       </c>
       <c r="D54">
-        <v>0.261</v>
+        <v>0.26</v>
       </c>
       <c r="E54">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F54">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G54">
         <v>4</v>
@@ -1857,16 +1857,16 @@
         <v>10</v>
       </c>
       <c r="C55">
-        <v>1.251</v>
+        <v>1.25</v>
       </c>
       <c r="D55">
-        <v>0.9581</v>
+        <v>0.96</v>
       </c>
       <c r="E55">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F55">
-        <v>2.502</v>
+        <v>2.5</v>
       </c>
       <c r="G55">
         <v>4</v>
@@ -1882,16 +1882,16 @@
         <v>67</v>
       </c>
       <c r="C56">
-        <v>1.555</v>
+        <v>1.55</v>
       </c>
       <c r="D56">
-        <v>1.643</v>
+        <v>1.64</v>
       </c>
       <c r="E56">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F56">
-        <v>6.892</v>
+        <v>6.89</v>
       </c>
       <c r="G56">
         <v>24</v>
@@ -1907,13 +1907,13 @@
         <v>33</v>
       </c>
       <c r="C57">
-        <v>4.294</v>
+        <v>4.29</v>
       </c>
       <c r="D57">
-        <v>4.247</v>
+        <v>4.25</v>
       </c>
       <c r="E57">
-        <v>0.592</v>
+        <v>0.59</v>
       </c>
       <c r="F57">
         <v>10.01</v>
@@ -1932,16 +1932,16 @@
         <v>39294</v>
       </c>
       <c r="C58">
-        <v>3.567</v>
+        <v>3.57</v>
       </c>
       <c r="D58">
-        <v>7.587</v>
+        <v>7.59</v>
       </c>
       <c r="E58">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F58">
-        <v>219.2</v>
+        <v>219.15</v>
       </c>
       <c r="G58">
         <v>6131</v>
@@ -1957,16 +1957,16 @@
         <v>45</v>
       </c>
       <c r="C59">
-        <v>1.899</v>
+        <v>1.9</v>
       </c>
       <c r="D59">
-        <v>2.244</v>
+        <v>2.24</v>
       </c>
       <c r="E59">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F59">
-        <v>9.131</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G59">
         <v>15</v>
@@ -1982,13 +1982,13 @@
         <v>16813</v>
       </c>
       <c r="C60">
-        <v>2.181</v>
+        <v>2.18</v>
       </c>
       <c r="D60">
-        <v>4.483</v>
+        <v>4.48</v>
       </c>
       <c r="E60">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F60">
         <v>81.17</v>
@@ -2007,13 +2007,13 @@
         <v>3827</v>
       </c>
       <c r="C61">
-        <v>2.258</v>
+        <v>2.26</v>
       </c>
       <c r="D61">
-        <v>3.817</v>
+        <v>3.82</v>
       </c>
       <c r="E61">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F61">
         <v>49.08</v>
@@ -2032,16 +2032,16 @@
         <v>15</v>
       </c>
       <c r="C62">
-        <v>2.502</v>
+        <v>2.5</v>
       </c>
       <c r="D62">
-        <v>2.293</v>
+        <v>2.29</v>
       </c>
       <c r="E62">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F62">
-        <v>5.003</v>
+        <v>5</v>
       </c>
       <c r="G62">
         <v>3</v>
@@ -2057,16 +2057,16 @@
         <v>19</v>
       </c>
       <c r="C63">
-        <v>2.381</v>
+        <v>2.38</v>
       </c>
       <c r="D63">
-        <v>1.159</v>
+        <v>1.16</v>
       </c>
       <c r="E63">
-        <v>1.501</v>
+        <v>1.5</v>
       </c>
       <c r="F63">
-        <v>4.357</v>
+        <v>4.36</v>
       </c>
       <c r="G63">
         <v>5</v>
@@ -2082,13 +2082,13 @@
         <v>18083</v>
       </c>
       <c r="C64">
-        <v>2.157</v>
+        <v>2.16</v>
       </c>
       <c r="D64">
-        <v>3.891</v>
+        <v>3.89</v>
       </c>
       <c r="E64">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F64">
         <v>91.31</v>
@@ -2107,16 +2107,16 @@
         <v>175</v>
       </c>
       <c r="C65">
-        <v>1.738</v>
+        <v>1.74</v>
       </c>
       <c r="D65">
-        <v>1.641</v>
+        <v>1.64</v>
       </c>
       <c r="E65">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F65">
-        <v>7.689</v>
+        <v>7.69</v>
       </c>
       <c r="G65">
         <v>54</v>
@@ -2132,16 +2132,16 @@
         <v>4</v>
       </c>
       <c r="C66">
-        <v>0.6994</v>
+        <v>0.7</v>
       </c>
       <c r="D66">
-        <v>0.2687</v>
+        <v>0.27</v>
       </c>
       <c r="E66">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F66">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G66">
         <v>3</v>
@@ -2157,13 +2157,13 @@
         <v>10063</v>
       </c>
       <c r="C67">
-        <v>2.287</v>
+        <v>2.29</v>
       </c>
       <c r="D67">
-        <v>4.895</v>
+        <v>4.9</v>
       </c>
       <c r="E67">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F67">
         <v>146.1</v>
@@ -2185,10 +2185,10 @@
         <v>2.84</v>
       </c>
       <c r="D68">
-        <v>5.162</v>
+        <v>5.16</v>
       </c>
       <c r="E68">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F68">
         <v>19.48</v>
@@ -2207,16 +2207,16 @@
         <v>52</v>
       </c>
       <c r="C69">
-        <v>0.9647</v>
+        <v>0.96</v>
       </c>
       <c r="D69">
-        <v>1.274</v>
+        <v>1.27</v>
       </c>
       <c r="E69">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F69">
-        <v>5.727</v>
+        <v>5.73</v>
       </c>
       <c r="G69">
         <v>28</v>
@@ -2279,13 +2279,13 @@
         <v>523</v>
       </c>
       <c r="C2">
-        <v>1.893</v>
+        <v>1.89</v>
       </c>
       <c r="D2">
-        <v>2.548</v>
+        <v>2.55</v>
       </c>
       <c r="E2">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F2">
         <v>16.79</v>
@@ -2310,7 +2310,7 @@
         <v>6.64</v>
       </c>
       <c r="E3">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F3">
         <v>26.09</v>
@@ -2329,16 +2329,16 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>1.128</v>
+        <v>1.13</v>
       </c>
       <c r="D4">
-        <v>0.8203</v>
+        <v>0.82</v>
       </c>
       <c r="E4">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F4">
-        <v>2.502</v>
+        <v>2.5</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2354,16 +2354,16 @@
         <v>16</v>
       </c>
       <c r="C5">
-        <v>1.334</v>
+        <v>1.33</v>
       </c>
       <c r="D5">
-        <v>0.7533</v>
+        <v>0.75</v>
       </c>
       <c r="E5">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F5">
-        <v>2.502</v>
+        <v>2.5</v>
       </c>
       <c r="G5">
         <v>6</v>
@@ -2379,13 +2379,13 @@
         <v>397</v>
       </c>
       <c r="C6">
-        <v>1.348</v>
+        <v>1.35</v>
       </c>
       <c r="D6">
-        <v>1.734</v>
+        <v>1.73</v>
       </c>
       <c r="E6">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
         <v>10.98</v>
@@ -2404,13 +2404,13 @@
         <v>2917</v>
       </c>
       <c r="C7">
-        <v>2.762</v>
+        <v>2.76</v>
       </c>
       <c r="D7">
-        <v>5.586</v>
+        <v>5.59</v>
       </c>
       <c r="E7">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F7">
         <v>79.40000000000001</v>
@@ -2429,13 +2429,13 @@
         <v>3226</v>
       </c>
       <c r="C8">
-        <v>2.055</v>
+        <v>2.06</v>
       </c>
       <c r="D8">
-        <v>3.593</v>
+        <v>3.59</v>
       </c>
       <c r="E8">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
         <v>40.58</v>
@@ -2457,10 +2457,10 @@
         <v>1.77</v>
       </c>
       <c r="D9">
-        <v>4.132</v>
+        <v>4.13</v>
       </c>
       <c r="E9">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F9">
         <v>34.6</v>
@@ -2479,13 +2479,13 @@
         <v>1</v>
       </c>
       <c r="C10">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="E10">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F10">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="G10">
         <v>1</v>
@@ -2501,16 +2501,16 @@
         <v>3</v>
       </c>
       <c r="C11">
-        <v>1.198</v>
+        <v>1.2</v>
       </c>
       <c r="D11">
-        <v>2.438</v>
+        <v>2.44</v>
       </c>
       <c r="E11">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F11">
-        <v>3.949</v>
+        <v>3.95</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -2526,16 +2526,16 @@
         <v>45</v>
       </c>
       <c r="C12">
-        <v>1.193</v>
+        <v>1.19</v>
       </c>
       <c r="D12">
-        <v>1.734</v>
+        <v>1.73</v>
       </c>
       <c r="E12">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F12">
-        <v>8.569000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="G12">
         <v>21</v>
@@ -2551,16 +2551,16 @@
         <v>142</v>
       </c>
       <c r="C13">
-        <v>1.031</v>
+        <v>1.03</v>
       </c>
       <c r="D13">
-        <v>1.047</v>
+        <v>1.05</v>
       </c>
       <c r="E13">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F13">
-        <v>5.504</v>
+        <v>5.5</v>
       </c>
       <c r="G13">
         <v>74</v>
@@ -2576,16 +2576,16 @@
         <v>3</v>
       </c>
       <c r="C14">
-        <v>0.6657</v>
+        <v>0.67</v>
       </c>
       <c r="D14">
-        <v>0.8449</v>
+        <v>0.84</v>
       </c>
       <c r="E14">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F14">
-        <v>1.964</v>
+        <v>1.96</v>
       </c>
       <c r="G14">
         <v>3</v>
@@ -2601,16 +2601,16 @@
         <v>7</v>
       </c>
       <c r="C15">
-        <v>0.7005</v>
+        <v>0.7</v>
       </c>
       <c r="D15">
-        <v>0.274</v>
+        <v>0.27</v>
       </c>
       <c r="E15">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F15">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -2626,16 +2626,16 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>0.6041</v>
+        <v>0.6</v>
       </c>
       <c r="D16">
-        <v>0.2004</v>
+        <v>0.2</v>
       </c>
       <c r="E16">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F16">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>6</v>
@@ -2651,16 +2651,16 @@
         <v>139</v>
       </c>
       <c r="C17">
-        <v>1.543</v>
+        <v>1.54</v>
       </c>
       <c r="D17">
         <v>1.12</v>
       </c>
       <c r="E17">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F17">
-        <v>5.003</v>
+        <v>5</v>
       </c>
       <c r="G17">
         <v>46</v>
@@ -2676,16 +2676,16 @@
         <v>2</v>
       </c>
       <c r="C18">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F18">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="G18">
         <v>2</v>
@@ -2701,16 +2701,16 @@
         <v>19</v>
       </c>
       <c r="C19">
-        <v>1.901</v>
+        <v>1.9</v>
       </c>
       <c r="D19">
-        <v>2.105</v>
+        <v>2.11</v>
       </c>
       <c r="E19">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F19">
-        <v>5.504</v>
+        <v>5.5</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -2726,13 +2726,13 @@
         <v>143</v>
       </c>
       <c r="C20">
-        <v>1.646</v>
+        <v>1.65</v>
       </c>
       <c r="D20">
-        <v>2.113</v>
+        <v>2.11</v>
       </c>
       <c r="E20">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F20">
         <v>10.01</v>
@@ -2751,16 +2751,16 @@
         <v>21527</v>
       </c>
       <c r="C21">
-        <v>2.457</v>
+        <v>2.46</v>
       </c>
       <c r="D21">
         <v>5.31</v>
       </c>
       <c r="E21">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F21">
-        <v>162</v>
+        <v>162.05</v>
       </c>
       <c r="G21">
         <v>4812</v>
@@ -2776,16 +2776,16 @@
         <v>59323</v>
       </c>
       <c r="C22">
-        <v>2.763</v>
+        <v>2.76</v>
       </c>
       <c r="D22">
-        <v>5.351</v>
+        <v>5.35</v>
       </c>
       <c r="E22">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F22">
-        <v>186.4</v>
+        <v>186.45</v>
       </c>
       <c r="G22">
         <v>11772</v>
@@ -2801,13 +2801,13 @@
         <v>2474</v>
       </c>
       <c r="C23">
-        <v>2.621</v>
+        <v>2.62</v>
       </c>
       <c r="D23">
-        <v>5.868</v>
+        <v>5.87</v>
       </c>
       <c r="E23">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F23">
         <v>60.88</v>
@@ -2826,13 +2826,13 @@
         <v>178</v>
       </c>
       <c r="C24">
-        <v>2.586</v>
+        <v>2.59</v>
       </c>
       <c r="D24">
-        <v>3.346</v>
+        <v>3.35</v>
       </c>
       <c r="E24">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F24">
         <v>15.01</v>
@@ -2851,13 +2851,13 @@
         <v>248</v>
       </c>
       <c r="C25">
-        <v>3.346</v>
+        <v>3.35</v>
       </c>
       <c r="D25">
-        <v>8.451000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="E25">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F25">
         <v>54.11</v>
@@ -2876,16 +2876,16 @@
         <v>110</v>
       </c>
       <c r="C26">
-        <v>0.7958</v>
+        <v>0.8</v>
       </c>
       <c r="D26">
-        <v>1.093</v>
+        <v>1.09</v>
       </c>
       <c r="E26">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F26">
-        <v>7.689</v>
+        <v>7.69</v>
       </c>
       <c r="G26">
         <v>76</v>
@@ -2901,13 +2901,13 @@
         <v>1</v>
       </c>
       <c r="C27">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="E27">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F27">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -2923,13 +2923,13 @@
         <v>1</v>
       </c>
       <c r="C28">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="E28">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F28">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -2945,13 +2945,13 @@
         <v>2262</v>
       </c>
       <c r="C29">
-        <v>2.119</v>
+        <v>2.12</v>
       </c>
       <c r="D29">
-        <v>2.763</v>
+        <v>2.76</v>
       </c>
       <c r="E29">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F29">
         <v>19.51</v>
@@ -2970,13 +2970,13 @@
         <v>16737</v>
       </c>
       <c r="C30">
-        <v>1.677</v>
+        <v>1.68</v>
       </c>
       <c r="D30">
-        <v>4.455</v>
+        <v>4.46</v>
       </c>
       <c r="E30">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F30">
         <v>146.1</v>
@@ -3001,10 +3001,10 @@
         <v>13.73</v>
       </c>
       <c r="E31">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F31">
-        <v>365.2</v>
+        <v>365.25</v>
       </c>
       <c r="G31">
         <v>23947</v>
@@ -3026,7 +3026,7 @@
         <v>14.9</v>
       </c>
       <c r="E32">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F32">
         <v>730.5</v>
@@ -3048,13 +3048,13 @@
         <v>1.93</v>
       </c>
       <c r="D33">
-        <v>2.258</v>
+        <v>2.26</v>
       </c>
       <c r="E33">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F33">
-        <v>6.012</v>
+        <v>6.01</v>
       </c>
       <c r="G33">
         <v>5</v>
@@ -3070,16 +3070,16 @@
         <v>7106</v>
       </c>
       <c r="C34">
-        <v>2.069</v>
+        <v>2.07</v>
       </c>
       <c r="D34">
-        <v>5.968</v>
+        <v>5.97</v>
       </c>
       <c r="E34">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F34">
-        <v>137</v>
+        <v>136.97</v>
       </c>
       <c r="G34">
         <v>1851</v>
@@ -3095,16 +3095,16 @@
         <v>93</v>
       </c>
       <c r="C35">
-        <v>1.089</v>
+        <v>1.09</v>
       </c>
       <c r="D35">
-        <v>1.505</v>
+        <v>1.5</v>
       </c>
       <c r="E35">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F35">
-        <v>8.909000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="G35">
         <v>47</v>
@@ -3120,13 +3120,13 @@
         <v>1352</v>
       </c>
       <c r="C36">
-        <v>1.891</v>
+        <v>1.89</v>
       </c>
       <c r="D36">
-        <v>3.217</v>
+        <v>3.22</v>
       </c>
       <c r="E36">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F36">
         <v>28.1</v>
@@ -3145,16 +3145,16 @@
         <v>7</v>
       </c>
       <c r="C37">
-        <v>0.5837</v>
+        <v>0.58</v>
       </c>
       <c r="D37">
-        <v>0.2043</v>
+        <v>0.2</v>
       </c>
       <c r="E37">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F37">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G37">
         <v>6</v>
@@ -3170,13 +3170,13 @@
         <v>221</v>
       </c>
       <c r="C38">
-        <v>2.895</v>
+        <v>2.89</v>
       </c>
       <c r="D38">
-        <v>6.115</v>
+        <v>6.12</v>
       </c>
       <c r="E38">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F38">
         <v>32.23</v>
@@ -3195,13 +3195,13 @@
         <v>2</v>
       </c>
       <c r="C39">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="F39">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G39">
         <v>1</v>
@@ -3245,10 +3245,10 @@
         <v>2</v>
       </c>
       <c r="D41">
-        <v>3.089</v>
+        <v>3.09</v>
       </c>
       <c r="E41">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F41">
         <v>34.02</v>
@@ -3267,16 +3267,16 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>0.7428</v>
+        <v>0.74</v>
       </c>
       <c r="D42">
-        <v>0.543</v>
+        <v>0.54</v>
       </c>
       <c r="E42">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F42">
-        <v>1.441</v>
+        <v>1.44</v>
       </c>
       <c r="G42">
         <v>3</v>
@@ -3292,16 +3292,16 @@
         <v>3</v>
       </c>
       <c r="C43">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F43">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="G43">
         <v>3</v>
@@ -3317,13 +3317,13 @@
         <v>135</v>
       </c>
       <c r="C44">
-        <v>7.395</v>
+        <v>7.39</v>
       </c>
       <c r="D44">
         <v>20.24</v>
       </c>
       <c r="E44">
-        <v>3.502</v>
+        <v>3.5</v>
       </c>
       <c r="F44">
         <v>74.70999999999999</v>
@@ -3342,13 +3342,13 @@
         <v>484</v>
       </c>
       <c r="C45">
-        <v>1.934</v>
+        <v>1.93</v>
       </c>
       <c r="D45">
-        <v>2.949</v>
+        <v>2.95</v>
       </c>
       <c r="E45">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F45">
         <v>19.73</v>
@@ -3367,16 +3367,16 @@
         <v>5</v>
       </c>
       <c r="C46">
-        <v>2.624</v>
+        <v>2.62</v>
       </c>
       <c r="D46">
-        <v>0.2774</v>
+        <v>0.28</v>
       </c>
       <c r="E46">
-        <v>2.403</v>
+        <v>2.4</v>
       </c>
       <c r="F46">
-        <v>2.795</v>
+        <v>2.8</v>
       </c>
       <c r="G46">
         <v>2</v>
@@ -3395,10 +3395,10 @@
         <v>1.37</v>
       </c>
       <c r="D47">
-        <v>2.415</v>
+        <v>2.42</v>
       </c>
       <c r="E47">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F47">
         <v>20.29</v>
@@ -3417,16 +3417,16 @@
         <v>13</v>
       </c>
       <c r="C48">
-        <v>0.9892</v>
+        <v>0.99</v>
       </c>
       <c r="D48">
-        <v>1.156</v>
+        <v>1.16</v>
       </c>
       <c r="E48">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F48">
-        <v>3.176</v>
+        <v>3.18</v>
       </c>
       <c r="G48">
         <v>8</v>
@@ -3448,7 +3448,7 @@
         <v>2.23</v>
       </c>
       <c r="E49">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F49">
         <v>12.95</v>
@@ -3467,16 +3467,16 @@
         <v>5</v>
       </c>
       <c r="C50">
-        <v>0.7145</v>
+        <v>0.71</v>
       </c>
       <c r="D50">
-        <v>0.2881</v>
+        <v>0.29</v>
       </c>
       <c r="E50">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F50">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G50">
         <v>4</v>
@@ -3492,16 +3492,16 @@
         <v>792</v>
       </c>
       <c r="C51">
-        <v>1.528</v>
+        <v>1.53</v>
       </c>
       <c r="D51">
-        <v>1.508</v>
+        <v>1.51</v>
       </c>
       <c r="E51">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F51">
-        <v>8.506</v>
+        <v>8.51</v>
       </c>
       <c r="G51">
         <v>269</v>
@@ -3517,16 +3517,16 @@
         <v>23</v>
       </c>
       <c r="C52">
-        <v>0.8126</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D52">
-        <v>0.3531</v>
+        <v>0.35</v>
       </c>
       <c r="E52">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F52">
-        <v>1.501</v>
+        <v>1.5</v>
       </c>
       <c r="G52">
         <v>15</v>
@@ -3542,16 +3542,16 @@
         <v>59</v>
       </c>
       <c r="C53">
-        <v>0.9546</v>
+        <v>0.95</v>
       </c>
       <c r="D53">
-        <v>0.5603</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E53">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F53">
-        <v>2.502</v>
+        <v>2.5</v>
       </c>
       <c r="G53">
         <v>32</v>
@@ -3567,13 +3567,13 @@
         <v>374</v>
       </c>
       <c r="C54">
-        <v>1.631</v>
+        <v>1.63</v>
       </c>
       <c r="D54">
-        <v>2.024</v>
+        <v>2.02</v>
       </c>
       <c r="E54">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F54">
         <v>14.05</v>
@@ -3592,16 +3592,16 @@
         <v>5</v>
       </c>
       <c r="C55">
-        <v>0.7024</v>
+        <v>0.7</v>
       </c>
       <c r="D55">
-        <v>0.261</v>
+        <v>0.26</v>
       </c>
       <c r="E55">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F55">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G55">
         <v>4</v>
@@ -3617,16 +3617,16 @@
         <v>10</v>
       </c>
       <c r="C56">
-        <v>1.251</v>
+        <v>1.25</v>
       </c>
       <c r="D56">
-        <v>0.9581</v>
+        <v>0.96</v>
       </c>
       <c r="E56">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F56">
-        <v>2.502</v>
+        <v>2.5</v>
       </c>
       <c r="G56">
         <v>4</v>
@@ -3642,16 +3642,16 @@
         <v>67</v>
       </c>
       <c r="C57">
-        <v>1.555</v>
+        <v>1.55</v>
       </c>
       <c r="D57">
-        <v>1.643</v>
+        <v>1.64</v>
       </c>
       <c r="E57">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F57">
-        <v>6.892</v>
+        <v>6.89</v>
       </c>
       <c r="G57">
         <v>24</v>
@@ -3667,13 +3667,13 @@
         <v>33</v>
       </c>
       <c r="C58">
-        <v>4.294</v>
+        <v>4.29</v>
       </c>
       <c r="D58">
-        <v>4.247</v>
+        <v>4.25</v>
       </c>
       <c r="E58">
-        <v>0.592</v>
+        <v>0.59</v>
       </c>
       <c r="F58">
         <v>10.01</v>
@@ -3692,16 +3692,16 @@
         <v>39294</v>
       </c>
       <c r="C59">
-        <v>3.567</v>
+        <v>3.57</v>
       </c>
       <c r="D59">
-        <v>7.587</v>
+        <v>7.59</v>
       </c>
       <c r="E59">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F59">
-        <v>219.2</v>
+        <v>219.15</v>
       </c>
       <c r="G59">
         <v>6131</v>
@@ -3717,16 +3717,16 @@
         <v>45</v>
       </c>
       <c r="C60">
-        <v>1.899</v>
+        <v>1.9</v>
       </c>
       <c r="D60">
-        <v>2.244</v>
+        <v>2.24</v>
       </c>
       <c r="E60">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F60">
-        <v>9.131</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="G60">
         <v>15</v>
@@ -3742,13 +3742,13 @@
         <v>16813</v>
       </c>
       <c r="C61">
-        <v>2.181</v>
+        <v>2.18</v>
       </c>
       <c r="D61">
-        <v>4.483</v>
+        <v>4.48</v>
       </c>
       <c r="E61">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F61">
         <v>81.17</v>
@@ -3767,13 +3767,13 @@
         <v>3827</v>
       </c>
       <c r="C62">
-        <v>2.258</v>
+        <v>2.26</v>
       </c>
       <c r="D62">
-        <v>3.817</v>
+        <v>3.82</v>
       </c>
       <c r="E62">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F62">
         <v>49.08</v>
@@ -3792,16 +3792,16 @@
         <v>15</v>
       </c>
       <c r="C63">
-        <v>2.502</v>
+        <v>2.5</v>
       </c>
       <c r="D63">
-        <v>2.293</v>
+        <v>2.29</v>
       </c>
       <c r="E63">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F63">
-        <v>5.003</v>
+        <v>5</v>
       </c>
       <c r="G63">
         <v>3</v>
@@ -3817,16 +3817,16 @@
         <v>19</v>
       </c>
       <c r="C64">
-        <v>2.381</v>
+        <v>2.38</v>
       </c>
       <c r="D64">
-        <v>1.159</v>
+        <v>1.16</v>
       </c>
       <c r="E64">
-        <v>1.501</v>
+        <v>1.5</v>
       </c>
       <c r="F64">
-        <v>4.357</v>
+        <v>4.36</v>
       </c>
       <c r="G64">
         <v>5</v>
@@ -3842,13 +3842,13 @@
         <v>18083</v>
       </c>
       <c r="C65">
-        <v>2.157</v>
+        <v>2.16</v>
       </c>
       <c r="D65">
-        <v>3.891</v>
+        <v>3.89</v>
       </c>
       <c r="E65">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F65">
         <v>91.31</v>
@@ -3867,16 +3867,16 @@
         <v>175</v>
       </c>
       <c r="C66">
-        <v>1.738</v>
+        <v>1.74</v>
       </c>
       <c r="D66">
-        <v>1.641</v>
+        <v>1.64</v>
       </c>
       <c r="E66">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F66">
-        <v>7.689</v>
+        <v>7.69</v>
       </c>
       <c r="G66">
         <v>54</v>
@@ -3892,16 +3892,16 @@
         <v>4</v>
       </c>
       <c r="C67">
-        <v>0.6994</v>
+        <v>0.7</v>
       </c>
       <c r="D67">
-        <v>0.2687</v>
+        <v>0.27</v>
       </c>
       <c r="E67">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F67">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="G67">
         <v>3</v>
@@ -3917,13 +3917,13 @@
         <v>10063</v>
       </c>
       <c r="C68">
-        <v>2.287</v>
+        <v>2.29</v>
       </c>
       <c r="D68">
-        <v>4.895</v>
+        <v>4.9</v>
       </c>
       <c r="E68">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F68">
         <v>146.1</v>
@@ -3945,10 +3945,10 @@
         <v>2.84</v>
       </c>
       <c r="D69">
-        <v>5.162</v>
+        <v>5.16</v>
       </c>
       <c r="E69">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F69">
         <v>19.48</v>
@@ -3967,16 +3967,16 @@
         <v>52</v>
       </c>
       <c r="C70">
-        <v>0.9647</v>
+        <v>0.96</v>
       </c>
       <c r="D70">
-        <v>1.274</v>
+        <v>1.27</v>
       </c>
       <c r="E70">
-        <v>0.5003</v>
+        <v>0.5</v>
       </c>
       <c r="F70">
-        <v>5.727</v>
+        <v>5.73</v>
       </c>
       <c r="G70">
         <v>28</v>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
@@ -11,6 +11,10 @@
     <sheet name="all_summary_statistics" sheetId="2" r:id="rId2"/>
     <sheet name="user_only_summary" sheetId="3" r:id="rId3"/>
     <sheet name="all_summary" sheetId="4" r:id="rId4"/>
+    <sheet name="user_only_summary_statistics_" sheetId="5" r:id="rId5"/>
+    <sheet name="all_summary_statistics_reduce" sheetId="6" r:id="rId6"/>
+    <sheet name="user_only_summary_reduced" sheetId="7" r:id="rId7"/>
+    <sheet name="all_summary_reduced" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3210,7 +3214,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Not_clinically_relevant</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B40">
@@ -3980,6 +3984,415 @@
       </c>
       <c r="G70">
         <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visit_per_year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>min_visit_per_year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>max_visit_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_visit_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>median_visit_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>lower_q_visits_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>upper_q_visits_per_year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>16.13</v>
+      </c>
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+      <c r="C2">
+        <v>730.5</v>
+      </c>
+      <c r="D2">
+        <v>20.52</v>
+      </c>
+      <c r="E2">
+        <v>13.51</v>
+      </c>
+      <c r="F2">
+        <v>7.51</v>
+      </c>
+      <c r="G2">
+        <v>23.02</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visit_per_year</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>min_visit_per_year</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>max_visit_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_visit_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>median_visit_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>lower_q_visits_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>upper_q_visits_per_year</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>15.98</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+      <c r="C2">
+        <v>730.5</v>
+      </c>
+      <c r="D2">
+        <v>20.48</v>
+      </c>
+      <c r="E2">
+        <v>13.01</v>
+      </c>
+      <c r="F2">
+        <v>7.51</v>
+      </c>
+      <c r="G2">
+        <v>22.63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>specialty_reduced</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_visits</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visits_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_visits_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>min_visits_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>max_visits_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>num_subjects_visited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>General Practitioner</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>560692</v>
+      </c>
+      <c r="C2">
+        <v>13.34</v>
+      </c>
+      <c r="D2">
+        <v>16.52</v>
+      </c>
+      <c r="E2">
+        <v>0.5</v>
+      </c>
+      <c r="F2">
+        <v>365.25</v>
+      </c>
+      <c r="G2">
+        <v>24444</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Nurse</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>61573</v>
+      </c>
+      <c r="C3">
+        <v>2.86</v>
+      </c>
+      <c r="D3">
+        <v>5.24</v>
+      </c>
+      <c r="E3">
+        <v>0.5</v>
+      </c>
+      <c r="F3">
+        <v>162.05</v>
+      </c>
+      <c r="G3">
+        <v>11836</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>58169</v>
+      </c>
+      <c r="C4">
+        <v>4.18</v>
+      </c>
+      <c r="D4">
+        <v>13.28</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+      <c r="F4">
+        <v>730.5</v>
+      </c>
+      <c r="G4">
+        <v>7908</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>specialty_reduced</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>tot_visits</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>mean_visits_per_year</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sd_visits_per_year</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>min_visits_per_year</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>max_visits_per_year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>num_subjects_visited</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>General Practitioner</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>560692</v>
+      </c>
+      <c r="C2">
+        <v>13.34</v>
+      </c>
+      <c r="D2">
+        <v>16.52</v>
+      </c>
+      <c r="E2">
+        <v>0.5</v>
+      </c>
+      <c r="F2">
+        <v>365.25</v>
+      </c>
+      <c r="G2">
+        <v>24444</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Not Clinically Relevant</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Nurse</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>61573</v>
+      </c>
+      <c r="C4">
+        <v>2.86</v>
+      </c>
+      <c r="D4">
+        <v>5.24</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+      <c r="F4">
+        <v>162.05</v>
+      </c>
+      <c r="G4">
+        <v>11836</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>58169</v>
+      </c>
+      <c r="C5">
+        <v>4.18</v>
+      </c>
+      <c r="D5">
+        <v>13.28</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>730.5</v>
+      </c>
+      <c r="G5">
+        <v>7908</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
@@ -504,7 +504,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>14.11</v>
+        <v>7.06</v>
       </c>
       <c r="C3">
         <v>0.5</v>
@@ -652,25 +652,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>30.7</v>
+        <v>16.15</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>426</v>
+        <v>298</v>
       </c>
       <c r="E2">
-        <v>24.03</v>
+        <v>14.33</v>
       </c>
       <c r="F2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -678,25 +678,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>24.23</v>
+        <v>6.84</v>
       </c>
       <c r="C3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>166</v>
+        <v>95.5</v>
       </c>
       <c r="E3">
-        <v>11.08</v>
+        <v>6.54</v>
       </c>
       <c r="F3">
+        <v>5</v>
+      </c>
+      <c r="G3">
+        <v>2.5</v>
+      </c>
+      <c r="H3">
         <v>9</v>
-      </c>
-      <c r="G3">
-        <v>4.5</v>
-      </c>
-      <c r="H3">
-        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>334</v>
+        <v>222</v>
       </c>
       <c r="C2">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="D2">
-        <v>2.66</v>
+        <v>3.13</v>
       </c>
       <c r="E2">
         <v>0.5</v>
@@ -416,7 +416,7 @@
         <v>16.79</v>
       </c>
       <c r="G2">
-        <v>103</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -426,13 +426,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>1911</v>
+        <v>1641</v>
       </c>
       <c r="C3">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="D3">
-        <v>6.43</v>
+        <v>6.67</v>
       </c>
       <c r="E3">
         <v>0.5</v>
@@ -441,7 +441,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="G3">
-        <v>353</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4">
@@ -451,13 +451,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1994</v>
+        <v>1414</v>
       </c>
       <c r="C4">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="D4">
-        <v>4.38</v>
+        <v>4.47</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -466,7 +466,7 @@
         <v>44.54</v>
       </c>
       <c r="G4">
-        <v>532</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5">
@@ -476,13 +476,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="C5">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="D5">
-        <v>4.64</v>
+        <v>5.06</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -491,7 +491,7 @@
         <v>31.76</v>
       </c>
       <c r="G5">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="D6">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="E6">
         <v>0.5</v>
@@ -516,7 +516,7 @@
         <v>5.5</v>
       </c>
       <c r="G6">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -526,22 +526,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>2.13</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>2.36</v>
+        <v>0.87</v>
       </c>
       <c r="E7">
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="D8">
-        <v>1.72</v>
+        <v>1.02</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>8.720000000000001</v>
+        <v>3.88</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -576,13 +576,13 @@
         </is>
       </c>
       <c r="B9">
-        <v>13057</v>
+        <v>10752</v>
       </c>
       <c r="C9">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="D9">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="E9">
         <v>0.5</v>
@@ -591,7 +591,7 @@
         <v>98.06999999999999</v>
       </c>
       <c r="G9">
-        <v>3050</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="10">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B10">
-        <v>37173</v>
+        <v>31622</v>
       </c>
       <c r="C10">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="D10">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="E10">
         <v>0.5</v>
@@ -616,7 +616,7 @@
         <v>119.93</v>
       </c>
       <c r="G10">
-        <v>7679</v>
+        <v>6979</v>
       </c>
     </row>
     <row r="11">
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="B11">
-        <v>1559</v>
+        <v>1517</v>
       </c>
       <c r="C11">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="D11">
-        <v>6.79</v>
+        <v>6.89</v>
       </c>
       <c r="E11">
         <v>0.5</v>
@@ -641,7 +641,7 @@
         <v>50.73</v>
       </c>
       <c r="G11">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12">
@@ -651,22 +651,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="C12">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="D12">
-        <v>2.94</v>
+        <v>2.33</v>
       </c>
       <c r="E12">
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>11.51</v>
+        <v>9.51</v>
       </c>
       <c r="G12">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -676,13 +676,13 @@
         </is>
       </c>
       <c r="B13">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C13">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="D13">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="E13">
         <v>0.5</v>
@@ -691,7 +691,7 @@
         <v>7.69</v>
       </c>
       <c r="G13">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
@@ -701,13 +701,13 @@
         </is>
       </c>
       <c r="B14">
-        <v>10030</v>
+        <v>8450</v>
       </c>
       <c r="C14">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="D14">
-        <v>4.02</v>
+        <v>4.21</v>
       </c>
       <c r="E14">
         <v>0.5</v>
@@ -716,7 +716,7 @@
         <v>67.09</v>
       </c>
       <c r="G14">
-        <v>3457</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="15">
@@ -726,13 +726,13 @@
         </is>
       </c>
       <c r="B15">
-        <v>257149</v>
+        <v>218389</v>
       </c>
       <c r="C15">
-        <v>9.94</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="D15">
-        <v>12.08</v>
+        <v>12.21</v>
       </c>
       <c r="E15">
         <v>0.5</v>
@@ -741,7 +741,7 @@
         <v>166.11</v>
       </c>
       <c r="G15">
-        <v>16938</v>
+        <v>16407</v>
       </c>
     </row>
     <row r="16">
@@ -751,13 +751,13 @@
         </is>
       </c>
       <c r="B16">
-        <v>31182</v>
+        <v>28300</v>
       </c>
       <c r="C16">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="D16">
-        <v>10.75</v>
+        <v>10.93</v>
       </c>
       <c r="E16">
         <v>0.5</v>
@@ -766,7 +766,7 @@
         <v>111.43</v>
       </c>
       <c r="G16">
-        <v>4044</v>
+        <v>3837</v>
       </c>
     </row>
     <row r="17">
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B17">
-        <v>4339</v>
+        <v>3351</v>
       </c>
       <c r="C17">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="D17">
-        <v>4.8</v>
+        <v>5.13</v>
       </c>
       <c r="E17">
         <v>0.5</v>
@@ -791,7 +791,7 @@
         <v>69.56999999999999</v>
       </c>
       <c r="G17">
-        <v>1221</v>
+        <v>944</v>
       </c>
     </row>
     <row r="18">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="B18">
-        <v>934</v>
+        <v>674</v>
       </c>
       <c r="C18">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="D18">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="E18">
         <v>0.5</v>
@@ -816,7 +816,7 @@
         <v>23.56</v>
       </c>
       <c r="G18">
-        <v>242</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19">
@@ -851,13 +851,13 @@
         </is>
       </c>
       <c r="B20">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C20">
-        <v>3.27</v>
+        <v>3.74</v>
       </c>
       <c r="D20">
-        <v>6.94</v>
+        <v>7.21</v>
       </c>
       <c r="E20">
         <v>0.5</v>
@@ -866,7 +866,7 @@
         <v>32.23</v>
       </c>
       <c r="G20">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="B21">
-        <v>1560</v>
+        <v>1230</v>
       </c>
       <c r="C21">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="D21">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="E21">
         <v>0.5</v>
@@ -891,7 +891,7 @@
         <v>49.81</v>
       </c>
       <c r="G21">
-        <v>407</v>
+        <v>353</v>
       </c>
     </row>
     <row r="22">
@@ -901,13 +901,13 @@
         </is>
       </c>
       <c r="B22">
-        <v>314</v>
+        <v>243</v>
       </c>
       <c r="C22">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="D22">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="E22">
         <v>0.5</v>
@@ -916,7 +916,7 @@
         <v>12.51</v>
       </c>
       <c r="G22">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23">
@@ -926,13 +926,13 @@
         </is>
       </c>
       <c r="B23">
-        <v>351</v>
+        <v>174</v>
       </c>
       <c r="C23">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="D23">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="E23">
         <v>0.5</v>
@@ -941,7 +941,7 @@
         <v>18.73</v>
       </c>
       <c r="G23">
-        <v>138</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="B24">
-        <v>381</v>
+        <v>154</v>
       </c>
       <c r="C24">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="D24">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="E24">
         <v>0.5</v>
@@ -966,7 +966,7 @@
         <v>12.95</v>
       </c>
       <c r="G24">
-        <v>150</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B25">
-        <v>421</v>
+        <v>308</v>
       </c>
       <c r="C25">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="D25">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="E25">
         <v>0.5</v>
@@ -991,7 +991,7 @@
         <v>22</v>
       </c>
       <c r="G25">
-        <v>156</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26">
@@ -1001,13 +1001,13 @@
         </is>
       </c>
       <c r="B26">
-        <v>22522</v>
+        <v>17937</v>
       </c>
       <c r="C26">
-        <v>3.46</v>
+        <v>3.14</v>
       </c>
       <c r="D26">
-        <v>6.4</v>
+        <v>6.52</v>
       </c>
       <c r="E26">
         <v>0.5</v>
@@ -1016,7 +1016,7 @@
         <v>72.42</v>
       </c>
       <c r="G26">
-        <v>3917</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="27">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B27">
-        <v>10245</v>
+        <v>8872</v>
       </c>
       <c r="C27">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="D27">
-        <v>5.14</v>
+        <v>5.31</v>
       </c>
       <c r="E27">
         <v>0.5</v>
@@ -1041,7 +1041,7 @@
         <v>52.18</v>
       </c>
       <c r="G27">
-        <v>2662</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="28">
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="B28">
-        <v>2083</v>
+        <v>1719</v>
       </c>
       <c r="C28">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="D28">
-        <v>4.49</v>
+        <v>4.71</v>
       </c>
       <c r="E28">
         <v>0.5</v>
@@ -1066,7 +1066,7 @@
         <v>45.66</v>
       </c>
       <c r="G28">
-        <v>586</v>
+        <v>517</v>
       </c>
     </row>
     <row r="29">
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="B29">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C29">
-        <v>3.01</v>
+        <v>3.53</v>
       </c>
       <c r="D29">
-        <v>1.39</v>
+        <v>1.92</v>
       </c>
       <c r="E29">
         <v>1.65</v>
@@ -1091,7 +1091,7 @@
         <v>4.36</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="B30">
-        <v>10464</v>
+        <v>8210</v>
       </c>
       <c r="C30">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="D30">
-        <v>3.95</v>
+        <v>4.12</v>
       </c>
       <c r="E30">
         <v>0.5</v>
@@ -1116,7 +1116,7 @@
         <v>58.91</v>
       </c>
       <c r="G30">
-        <v>2824</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="31">
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="B31">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="C31">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="E31">
         <v>0.5</v>
@@ -1141,7 +1141,7 @@
         <v>11.78</v>
       </c>
       <c r="G31">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="B32">
-        <v>6360</v>
+        <v>5072</v>
       </c>
       <c r="C32">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="D32">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="E32">
         <v>0.5</v>
@@ -1166,7 +1166,7 @@
         <v>46.59</v>
       </c>
       <c r="G32">
-        <v>1559</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="33">
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>334</v>
+        <v>222</v>
       </c>
       <c r="C2">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="D2">
-        <v>2.66</v>
+        <v>3.13</v>
       </c>
       <c r="E2">
         <v>0.5</v>
@@ -1263,7 +1263,7 @@
         <v>16.79</v>
       </c>
       <c r="G2">
-        <v>103</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>1911</v>
+        <v>1641</v>
       </c>
       <c r="C3">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="D3">
-        <v>6.43</v>
+        <v>6.67</v>
       </c>
       <c r="E3">
         <v>0.5</v>
@@ -1288,7 +1288,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="G3">
-        <v>353</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4">
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1994</v>
+        <v>1414</v>
       </c>
       <c r="C4">
-        <v>2.11</v>
+        <v>1.87</v>
       </c>
       <c r="D4">
-        <v>4.38</v>
+        <v>4.47</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -1313,7 +1313,7 @@
         <v>44.54</v>
       </c>
       <c r="G4">
-        <v>532</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5">
@@ -1323,13 +1323,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>196</v>
+        <v>145</v>
       </c>
       <c r="C5">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="D5">
-        <v>4.64</v>
+        <v>5.06</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -1338,7 +1338,7 @@
         <v>31.76</v>
       </c>
       <c r="G5">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -1348,13 +1348,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="D6">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="E6">
         <v>0.5</v>
@@ -1363,7 +1363,7 @@
         <v>5.5</v>
       </c>
       <c r="G6">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C7">
-        <v>2.13</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>2.36</v>
+        <v>0.87</v>
       </c>
       <c r="E7">
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1398,22 +1398,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C8">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="D8">
-        <v>1.72</v>
+        <v>1.02</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>8.720000000000001</v>
+        <v>3.88</v>
       </c>
       <c r="G8">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="B9">
-        <v>13057</v>
+        <v>10752</v>
       </c>
       <c r="C9">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="D9">
-        <v>5.5</v>
+        <v>5.65</v>
       </c>
       <c r="E9">
         <v>0.5</v>
@@ -1438,7 +1438,7 @@
         <v>98.06999999999999</v>
       </c>
       <c r="G9">
-        <v>3050</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="10">
@@ -1448,13 +1448,13 @@
         </is>
       </c>
       <c r="B10">
-        <v>37173</v>
+        <v>31622</v>
       </c>
       <c r="C10">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="D10">
-        <v>5.2</v>
+        <v>5.24</v>
       </c>
       <c r="E10">
         <v>0.5</v>
@@ -1463,7 +1463,7 @@
         <v>119.93</v>
       </c>
       <c r="G10">
-        <v>7679</v>
+        <v>6979</v>
       </c>
     </row>
     <row r="11">
@@ -1473,13 +1473,13 @@
         </is>
       </c>
       <c r="B11">
-        <v>1559</v>
+        <v>1517</v>
       </c>
       <c r="C11">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="D11">
-        <v>6.79</v>
+        <v>6.89</v>
       </c>
       <c r="E11">
         <v>0.5</v>
@@ -1488,7 +1488,7 @@
         <v>50.73</v>
       </c>
       <c r="G11">
-        <v>366</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="C12">
-        <v>2.47</v>
+        <v>2.21</v>
       </c>
       <c r="D12">
-        <v>2.94</v>
+        <v>2.33</v>
       </c>
       <c r="E12">
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>11.51</v>
+        <v>9.51</v>
       </c>
       <c r="G12">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -1523,13 +1523,13 @@
         </is>
       </c>
       <c r="B13">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C13">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="D13">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="E13">
         <v>0.5</v>
@@ -1538,7 +1538,7 @@
         <v>7.69</v>
       </c>
       <c r="G13">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="B14">
-        <v>10030</v>
+        <v>8450</v>
       </c>
       <c r="C14">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="D14">
-        <v>4.02</v>
+        <v>4.21</v>
       </c>
       <c r="E14">
         <v>0.5</v>
@@ -1563,7 +1563,7 @@
         <v>67.09</v>
       </c>
       <c r="G14">
-        <v>3457</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="15">
@@ -1573,13 +1573,13 @@
         </is>
       </c>
       <c r="B15">
-        <v>257149</v>
+        <v>218389</v>
       </c>
       <c r="C15">
-        <v>9.94</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="D15">
-        <v>12.08</v>
+        <v>12.21</v>
       </c>
       <c r="E15">
         <v>0.5</v>
@@ -1588,7 +1588,7 @@
         <v>166.11</v>
       </c>
       <c r="G15">
-        <v>16938</v>
+        <v>16407</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         </is>
       </c>
       <c r="B16">
-        <v>31182</v>
+        <v>28300</v>
       </c>
       <c r="C16">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="D16">
-        <v>10.75</v>
+        <v>10.93</v>
       </c>
       <c r="E16">
         <v>0.5</v>
@@ -1613,7 +1613,7 @@
         <v>111.43</v>
       </c>
       <c r="G16">
-        <v>4044</v>
+        <v>3837</v>
       </c>
     </row>
     <row r="17">
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="B17">
-        <v>4339</v>
+        <v>3351</v>
       </c>
       <c r="C17">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="D17">
-        <v>4.8</v>
+        <v>5.13</v>
       </c>
       <c r="E17">
         <v>0.5</v>
@@ -1638,7 +1638,7 @@
         <v>69.56999999999999</v>
       </c>
       <c r="G17">
-        <v>1221</v>
+        <v>944</v>
       </c>
     </row>
     <row r="18">
@@ -1648,13 +1648,13 @@
         </is>
       </c>
       <c r="B18">
-        <v>934</v>
+        <v>674</v>
       </c>
       <c r="C18">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="D18">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="E18">
         <v>0.5</v>
@@ -1663,7 +1663,7 @@
         <v>23.56</v>
       </c>
       <c r="G18">
-        <v>242</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19">
@@ -1698,13 +1698,13 @@
         </is>
       </c>
       <c r="B20">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C20">
-        <v>3.27</v>
+        <v>3.74</v>
       </c>
       <c r="D20">
-        <v>6.94</v>
+        <v>7.21</v>
       </c>
       <c r="E20">
         <v>0.5</v>
@@ -1713,7 +1713,7 @@
         <v>32.23</v>
       </c>
       <c r="G20">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>494</v>
+        <v>822</v>
       </c>
     </row>
     <row r="22">
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="B22">
-        <v>1560</v>
+        <v>1230</v>
       </c>
       <c r="C22">
-        <v>2.11</v>
+        <v>1.95</v>
       </c>
       <c r="D22">
-        <v>4.02</v>
+        <v>4.06</v>
       </c>
       <c r="E22">
         <v>0.5</v>
@@ -1763,7 +1763,7 @@
         <v>49.81</v>
       </c>
       <c r="G22">
-        <v>407</v>
+        <v>353</v>
       </c>
     </row>
     <row r="23">
@@ -1773,13 +1773,13 @@
         </is>
       </c>
       <c r="B23">
-        <v>314</v>
+        <v>243</v>
       </c>
       <c r="C23">
-        <v>1.74</v>
+        <v>1.48</v>
       </c>
       <c r="D23">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="E23">
         <v>0.5</v>
@@ -1788,7 +1788,7 @@
         <v>12.51</v>
       </c>
       <c r="G23">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24">
@@ -1798,13 +1798,13 @@
         </is>
       </c>
       <c r="B24">
-        <v>351</v>
+        <v>174</v>
       </c>
       <c r="C24">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="D24">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="E24">
         <v>0.5</v>
@@ -1813,7 +1813,7 @@
         <v>18.73</v>
       </c>
       <c r="G24">
-        <v>138</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25">
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="B25">
-        <v>381</v>
+        <v>154</v>
       </c>
       <c r="C25">
-        <v>1.42</v>
+        <v>1.13</v>
       </c>
       <c r="D25">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="E25">
         <v>0.5</v>
@@ -1838,7 +1838,7 @@
         <v>12.95</v>
       </c>
       <c r="G25">
-        <v>150</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
@@ -1848,13 +1848,13 @@
         </is>
       </c>
       <c r="B26">
-        <v>421</v>
+        <v>308</v>
       </c>
       <c r="C26">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="D26">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="E26">
         <v>0.5</v>
@@ -1863,7 +1863,7 @@
         <v>22</v>
       </c>
       <c r="G26">
-        <v>156</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27">
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="B27">
-        <v>22522</v>
+        <v>17937</v>
       </c>
       <c r="C27">
-        <v>3.46</v>
+        <v>3.14</v>
       </c>
       <c r="D27">
-        <v>6.4</v>
+        <v>6.52</v>
       </c>
       <c r="E27">
         <v>0.5</v>
@@ -1888,7 +1888,7 @@
         <v>72.42</v>
       </c>
       <c r="G27">
-        <v>3917</v>
+        <v>3510</v>
       </c>
     </row>
     <row r="28">
@@ -1898,13 +1898,13 @@
         </is>
       </c>
       <c r="B28">
-        <v>10245</v>
+        <v>8872</v>
       </c>
       <c r="C28">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="D28">
-        <v>5.14</v>
+        <v>5.31</v>
       </c>
       <c r="E28">
         <v>0.5</v>
@@ -1913,7 +1913,7 @@
         <v>52.18</v>
       </c>
       <c r="G28">
-        <v>2662</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="29">
@@ -1923,13 +1923,13 @@
         </is>
       </c>
       <c r="B29">
-        <v>2083</v>
+        <v>1719</v>
       </c>
       <c r="C29">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="D29">
-        <v>4.49</v>
+        <v>4.71</v>
       </c>
       <c r="E29">
         <v>0.5</v>
@@ -1938,7 +1938,7 @@
         <v>45.66</v>
       </c>
       <c r="G29">
-        <v>586</v>
+        <v>517</v>
       </c>
     </row>
     <row r="30">
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="B30">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>3.01</v>
+        <v>3.53</v>
       </c>
       <c r="D30">
-        <v>1.39</v>
+        <v>1.92</v>
       </c>
       <c r="E30">
         <v>1.65</v>
@@ -1963,7 +1963,7 @@
         <v>4.36</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -1973,13 +1973,13 @@
         </is>
       </c>
       <c r="B31">
-        <v>10464</v>
+        <v>8210</v>
       </c>
       <c r="C31">
-        <v>2.11</v>
+        <v>1.99</v>
       </c>
       <c r="D31">
-        <v>3.95</v>
+        <v>4.12</v>
       </c>
       <c r="E31">
         <v>0.5</v>
@@ -1988,7 +1988,7 @@
         <v>58.91</v>
       </c>
       <c r="G31">
-        <v>2824</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="32">
@@ -1998,13 +1998,13 @@
         </is>
       </c>
       <c r="B32">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="C32">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="E32">
         <v>0.5</v>
@@ -2013,7 +2013,7 @@
         <v>11.78</v>
       </c>
       <c r="G32">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33">
@@ -2023,13 +2023,13 @@
         </is>
       </c>
       <c r="B33">
-        <v>6360</v>
+        <v>5072</v>
       </c>
       <c r="C33">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="D33">
-        <v>3.97</v>
+        <v>3.85</v>
       </c>
       <c r="E33">
         <v>0.5</v>
@@ -2038,7 +2038,7 @@
         <v>46.59</v>
       </c>
       <c r="G33">
-        <v>1559</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="34">
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>343369</v>
+        <v>290262</v>
       </c>
       <c r="C2">
-        <v>13.03</v>
+        <v>11.35</v>
       </c>
       <c r="D2">
-        <v>14.58</v>
+        <v>14.75</v>
       </c>
       <c r="E2">
         <v>0.5</v>
@@ -2135,7 +2135,7 @@
         <v>215.4</v>
       </c>
       <c r="G2">
-        <v>17453</v>
+        <v>17050</v>
       </c>
     </row>
     <row r="3">
@@ -2145,13 +2145,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>35745</v>
+        <v>28608</v>
       </c>
       <c r="C3">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="D3">
-        <v>5.3</v>
+        <v>5.38</v>
       </c>
       <c r="E3">
         <v>0.5</v>
@@ -2160,7 +2160,7 @@
         <v>98.56999999999999</v>
       </c>
       <c r="G3">
-        <v>7380</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="4">
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>36156</v>
+        <v>32143</v>
       </c>
       <c r="C4">
-        <v>4.41</v>
+        <v>4.32</v>
       </c>
       <c r="D4">
-        <v>10.05</v>
+        <v>10.32</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -2185,7 +2185,7 @@
         <v>111.43</v>
       </c>
       <c r="G4">
-        <v>5105</v>
+        <v>4718</v>
       </c>
     </row>
   </sheetData>
@@ -2242,13 +2242,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>343369</v>
+        <v>290262</v>
       </c>
       <c r="C2">
-        <v>13.03</v>
+        <v>11.35</v>
       </c>
       <c r="D2">
-        <v>14.58</v>
+        <v>14.75</v>
       </c>
       <c r="E2">
         <v>0.5</v>
@@ -2257,7 +2257,7 @@
         <v>215.4</v>
       </c>
       <c r="G2">
-        <v>17453</v>
+        <v>17050</v>
       </c>
     </row>
     <row r="3">
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>494</v>
+        <v>822</v>
       </c>
     </row>
     <row r="4">
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>35745</v>
+        <v>28608</v>
       </c>
       <c r="C4">
-        <v>2.79</v>
+        <v>2.57</v>
       </c>
       <c r="D4">
-        <v>5.3</v>
+        <v>5.38</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -2307,7 +2307,7 @@
         <v>98.56999999999999</v>
       </c>
       <c r="G4">
-        <v>7380</v>
+        <v>6507</v>
       </c>
     </row>
     <row r="5">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="B5">
-        <v>36156</v>
+        <v>32143</v>
       </c>
       <c r="C5">
-        <v>4.41</v>
+        <v>4.32</v>
       </c>
       <c r="D5">
-        <v>10.05</v>
+        <v>10.32</v>
       </c>
       <c r="E5">
         <v>0.5</v>
@@ -2332,7 +2332,7 @@
         <v>111.43</v>
       </c>
       <c r="G5">
-        <v>5105</v>
+        <v>4718</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
@@ -401,13 +401,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="C2">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="D2">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="E2">
         <v>0.5</v>
@@ -416,7 +416,7 @@
         <v>16.79</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -426,13 +426,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>1641</v>
+        <v>2122</v>
       </c>
       <c r="C3">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="D3">
-        <v>6.67</v>
+        <v>6.24</v>
       </c>
       <c r="E3">
         <v>0.5</v>
@@ -441,7 +441,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="G3">
-        <v>308</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4">
@@ -451,13 +451,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1414</v>
+        <v>1950</v>
       </c>
       <c r="C4">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="D4">
-        <v>4.47</v>
+        <v>4.19</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -466,7 +466,7 @@
         <v>44.54</v>
       </c>
       <c r="G4">
-        <v>435</v>
+        <v>627</v>
       </c>
     </row>
     <row r="5">
@@ -476,22 +476,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="C5">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="D5">
-        <v>5.06</v>
+        <v>5.27</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>31.76</v>
+        <v>34.6</v>
       </c>
       <c r="G5">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C6">
         <v>1.08</v>
       </c>
       <c r="D6">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="E6">
         <v>0.5</v>
@@ -516,7 +516,7 @@
         <v>5.5</v>
       </c>
       <c r="G6">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -526,13 +526,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0.87</v>
+        <v>0.71</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -541,7 +541,7 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="C8">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="D8">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>3.88</v>
+        <v>14.05</v>
       </c>
       <c r="G8">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -576,22 +576,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>10752</v>
+        <v>15343</v>
       </c>
       <c r="C9">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
       <c r="D9">
-        <v>5.65</v>
+        <v>5.93</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>98.06999999999999</v>
+        <v>162.05</v>
       </c>
       <c r="G9">
-        <v>2687</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="10">
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>31622</v>
+        <v>43287</v>
       </c>
       <c r="C10">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="D10">
-        <v>5.24</v>
+        <v>5.46</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>119.93</v>
+        <v>186.45</v>
       </c>
       <c r="G10">
-        <v>6979</v>
+        <v>9496</v>
       </c>
     </row>
     <row r="11">
@@ -626,22 +626,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>1517</v>
+        <v>2046</v>
       </c>
       <c r="C11">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="D11">
-        <v>6.89</v>
+        <v>5.91</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>50.73</v>
+        <v>45.66</v>
       </c>
       <c r="G11">
-        <v>354</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12">
@@ -651,22 +651,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="C12">
-        <v>2.21</v>
+        <v>2.66</v>
       </c>
       <c r="D12">
-        <v>2.33</v>
+        <v>3.21</v>
       </c>
       <c r="E12">
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>9.51</v>
+        <v>15.01</v>
       </c>
       <c r="G12">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -676,22 +676,22 @@
         </is>
       </c>
       <c r="B13">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C13">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="D13">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>7.69</v>
+        <v>8.82</v>
       </c>
       <c r="G13">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -701,22 +701,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>8450</v>
+        <v>11921</v>
       </c>
       <c r="C14">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="D14">
-        <v>4.21</v>
+        <v>3.76</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>67.09</v>
+        <v>71.27</v>
       </c>
       <c r="G14">
-        <v>3017</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="15">
@@ -726,10 +726,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>218389</v>
+        <v>303981</v>
       </c>
       <c r="C15">
-        <v>8.789999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="D15">
         <v>12.21</v>
@@ -741,7 +741,7 @@
         <v>166.11</v>
       </c>
       <c r="G15">
-        <v>16407</v>
+        <v>21488</v>
       </c>
     </row>
     <row r="16">
@@ -751,22 +751,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>28300</v>
+        <v>37858</v>
       </c>
       <c r="C16">
-        <v>4.75</v>
+        <v>5.14</v>
       </c>
       <c r="D16">
-        <v>10.93</v>
+        <v>9.69</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>111.43</v>
+        <v>112.76</v>
       </c>
       <c r="G16">
-        <v>3837</v>
+        <v>5023</v>
       </c>
     </row>
     <row r="17">
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="B17">
-        <v>3351</v>
+        <v>4765</v>
       </c>
       <c r="C17">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="D17">
-        <v>5.13</v>
+        <v>5.19</v>
       </c>
       <c r="E17">
         <v>0.5</v>
@@ -791,7 +791,7 @@
         <v>69.56999999999999</v>
       </c>
       <c r="G17">
-        <v>944</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="18">
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="B18">
-        <v>674</v>
+        <v>837</v>
       </c>
       <c r="C18">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="D18">
-        <v>3.29</v>
+        <v>3.57</v>
       </c>
       <c r="E18">
         <v>0.5</v>
@@ -816,7 +816,7 @@
         <v>23.56</v>
       </c>
       <c r="G18">
-        <v>197</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19">
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
         <v>0.5</v>
@@ -841,7 +841,7 @@
         <v>0.5</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -851,13 +851,13 @@
         </is>
       </c>
       <c r="B20">
-        <v>162</v>
+        <v>212</v>
       </c>
       <c r="C20">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="D20">
-        <v>7.21</v>
+        <v>6.36</v>
       </c>
       <c r="E20">
         <v>0.5</v>
@@ -866,7 +866,7 @@
         <v>32.23</v>
       </c>
       <c r="G20">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
@@ -876,22 +876,22 @@
         </is>
       </c>
       <c r="B21">
-        <v>1230</v>
+        <v>1580</v>
       </c>
       <c r="C21">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="D21">
-        <v>4.06</v>
+        <v>5.46</v>
       </c>
       <c r="E21">
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>49.81</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G21">
-        <v>353</v>
+        <v>468</v>
       </c>
     </row>
     <row r="22">
@@ -901,22 +901,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>243</v>
+        <v>334</v>
       </c>
       <c r="C22">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="D22">
-        <v>2.43</v>
+        <v>3.45</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>12.51</v>
+        <v>23.05</v>
       </c>
       <c r="G22">
-        <v>95</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23">
@@ -926,22 +926,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="C23">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="D23">
-        <v>2.55</v>
+        <v>3.27</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>18.73</v>
+        <v>22.14</v>
       </c>
       <c r="G23">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="B24">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="C24">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="D24">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="E24">
         <v>0.5</v>
@@ -966,7 +966,7 @@
         <v>12.95</v>
       </c>
       <c r="G24">
-        <v>82</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25">
@@ -976,22 +976,22 @@
         </is>
       </c>
       <c r="B25">
-        <v>308</v>
+        <v>474</v>
       </c>
       <c r="C25">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="D25">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="E25">
         <v>0.5</v>
       </c>
       <c r="F25">
-        <v>22</v>
+        <v>23.95</v>
       </c>
       <c r="G25">
-        <v>119</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26">
@@ -1001,22 +1001,22 @@
         </is>
       </c>
       <c r="B26">
-        <v>17937</v>
+        <v>26363</v>
       </c>
       <c r="C26">
-        <v>3.14</v>
+        <v>3.74</v>
       </c>
       <c r="D26">
-        <v>6.52</v>
+        <v>6.71</v>
       </c>
       <c r="E26">
         <v>0.5</v>
       </c>
       <c r="F26">
-        <v>72.42</v>
+        <v>81.17</v>
       </c>
       <c r="G26">
-        <v>3510</v>
+        <v>4903</v>
       </c>
     </row>
     <row r="27">
@@ -1026,22 +1026,22 @@
         </is>
       </c>
       <c r="B27">
-        <v>8872</v>
+        <v>12341</v>
       </c>
       <c r="C27">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="D27">
-        <v>5.31</v>
+        <v>4.75</v>
       </c>
       <c r="E27">
         <v>0.5</v>
       </c>
       <c r="F27">
-        <v>52.18</v>
+        <v>53.89</v>
       </c>
       <c r="G27">
-        <v>2372</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="28">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="B28">
-        <v>1719</v>
+        <v>2480</v>
       </c>
       <c r="C28">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="D28">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="E28">
         <v>0.5</v>
       </c>
       <c r="F28">
-        <v>45.66</v>
+        <v>52.54</v>
       </c>
       <c r="G28">
-        <v>517</v>
+        <v>702</v>
       </c>
     </row>
     <row r="29">
@@ -1101,22 +1101,22 @@
         </is>
       </c>
       <c r="B30">
-        <v>8210</v>
+        <v>11985</v>
       </c>
       <c r="C30">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="D30">
-        <v>4.12</v>
+        <v>4.29</v>
       </c>
       <c r="E30">
         <v>0.5</v>
       </c>
       <c r="F30">
-        <v>58.91</v>
+        <v>59.63</v>
       </c>
       <c r="G30">
-        <v>2393</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="31">
@@ -1126,22 +1126,22 @@
         </is>
       </c>
       <c r="B31">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="D31">
-        <v>2.22</v>
+        <v>3.78</v>
       </c>
       <c r="E31">
         <v>0.5</v>
       </c>
       <c r="F31">
-        <v>11.78</v>
+        <v>19.74</v>
       </c>
       <c r="G31">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32">
@@ -1151,22 +1151,22 @@
         </is>
       </c>
       <c r="B32">
-        <v>5072</v>
+        <v>7071</v>
       </c>
       <c r="C32">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="D32">
-        <v>3.85</v>
+        <v>5.83</v>
       </c>
       <c r="E32">
         <v>0.5</v>
       </c>
       <c r="F32">
-        <v>46.59</v>
+        <v>146.1</v>
       </c>
       <c r="G32">
-        <v>1335</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="33">
@@ -1176,22 +1176,22 @@
         </is>
       </c>
       <c r="B33">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C33">
-        <v>4.58</v>
+        <v>3.38</v>
       </c>
       <c r="D33">
-        <v>7.85</v>
+        <v>5.11</v>
       </c>
       <c r="E33">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F33">
-        <v>22.83</v>
+        <v>19.48</v>
       </c>
       <c r="G33">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1248,13 +1248,13 @@
         </is>
       </c>
       <c r="B2">
-        <v>222</v>
+        <v>267</v>
       </c>
       <c r="C2">
-        <v>1.94</v>
+        <v>2.21</v>
       </c>
       <c r="D2">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="E2">
         <v>0.5</v>
@@ -1263,7 +1263,7 @@
         <v>16.79</v>
       </c>
       <c r="G2">
-        <v>65</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -1273,13 +1273,13 @@
         </is>
       </c>
       <c r="B3">
-        <v>1641</v>
+        <v>2122</v>
       </c>
       <c r="C3">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="D3">
-        <v>6.67</v>
+        <v>6.24</v>
       </c>
       <c r="E3">
         <v>0.5</v>
@@ -1288,7 +1288,7 @@
         <v>79.40000000000001</v>
       </c>
       <c r="G3">
-        <v>308</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4">
@@ -1298,13 +1298,13 @@
         </is>
       </c>
       <c r="B4">
-        <v>1414</v>
+        <v>1950</v>
       </c>
       <c r="C4">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="D4">
-        <v>4.47</v>
+        <v>4.19</v>
       </c>
       <c r="E4">
         <v>0.5</v>
@@ -1313,7 +1313,7 @@
         <v>44.54</v>
       </c>
       <c r="G4">
-        <v>435</v>
+        <v>627</v>
       </c>
     </row>
     <row r="5">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>145</v>
+        <v>192</v>
       </c>
       <c r="C5">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="D5">
-        <v>5.06</v>
+        <v>5.27</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>31.76</v>
+        <v>34.6</v>
       </c>
       <c r="G5">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -1348,13 +1348,13 @@
         </is>
       </c>
       <c r="B6">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="C6">
         <v>1.08</v>
       </c>
       <c r="D6">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="E6">
         <v>0.5</v>
@@ -1363,7 +1363,7 @@
         <v>5.5</v>
       </c>
       <c r="G6">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="B7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>1</v>
       </c>
       <c r="D7">
-        <v>0.87</v>
+        <v>0.71</v>
       </c>
       <c r="E7">
         <v>0.5</v>
@@ -1388,7 +1388,7 @@
         <v>2</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -1398,22 +1398,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>49</v>
+        <v>90</v>
       </c>
       <c r="C8">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="D8">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>3.88</v>
+        <v>14.05</v>
       </c>
       <c r="G8">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>10752</v>
+        <v>15343</v>
       </c>
       <c r="C9">
-        <v>2.34</v>
+        <v>2.69</v>
       </c>
       <c r="D9">
-        <v>5.65</v>
+        <v>5.93</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>98.06999999999999</v>
+        <v>162.05</v>
       </c>
       <c r="G9">
-        <v>2687</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="10">
@@ -1448,22 +1448,22 @@
         </is>
       </c>
       <c r="B10">
-        <v>31622</v>
+        <v>43287</v>
       </c>
       <c r="C10">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="D10">
-        <v>5.24</v>
+        <v>5.46</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>119.93</v>
+        <v>186.45</v>
       </c>
       <c r="G10">
-        <v>6979</v>
+        <v>9496</v>
       </c>
     </row>
     <row r="11">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="B11">
-        <v>1517</v>
+        <v>2046</v>
       </c>
       <c r="C11">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="D11">
-        <v>6.89</v>
+        <v>5.91</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>50.73</v>
+        <v>45.66</v>
       </c>
       <c r="G11">
-        <v>354</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="B12">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="C12">
-        <v>2.21</v>
+        <v>2.66</v>
       </c>
       <c r="D12">
-        <v>2.33</v>
+        <v>3.21</v>
       </c>
       <c r="E12">
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>9.51</v>
+        <v>15.01</v>
       </c>
       <c r="G12">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="B13">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="C13">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="D13">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>7.69</v>
+        <v>8.82</v>
       </c>
       <c r="G13">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B14">
-        <v>8450</v>
+        <v>11921</v>
       </c>
       <c r="C14">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="D14">
-        <v>4.21</v>
+        <v>3.76</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>67.09</v>
+        <v>71.27</v>
       </c>
       <c r="G14">
-        <v>3017</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="15">
@@ -1573,10 +1573,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>218389</v>
+        <v>303981</v>
       </c>
       <c r="C15">
-        <v>8.789999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="D15">
         <v>12.21</v>
@@ -1588,7 +1588,7 @@
         <v>166.11</v>
       </c>
       <c r="G15">
-        <v>16407</v>
+        <v>21488</v>
       </c>
     </row>
     <row r="16">
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="B16">
-        <v>28300</v>
+        <v>37858</v>
       </c>
       <c r="C16">
-        <v>4.75</v>
+        <v>5.14</v>
       </c>
       <c r="D16">
-        <v>10.93</v>
+        <v>9.69</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>111.43</v>
+        <v>112.76</v>
       </c>
       <c r="G16">
-        <v>3837</v>
+        <v>5023</v>
       </c>
     </row>
     <row r="17">
@@ -1623,13 +1623,13 @@
         </is>
       </c>
       <c r="B17">
-        <v>3351</v>
+        <v>4765</v>
       </c>
       <c r="C17">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="D17">
-        <v>5.13</v>
+        <v>5.19</v>
       </c>
       <c r="E17">
         <v>0.5</v>
@@ -1638,7 +1638,7 @@
         <v>69.56999999999999</v>
       </c>
       <c r="G17">
-        <v>944</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="18">
@@ -1648,13 +1648,13 @@
         </is>
       </c>
       <c r="B18">
-        <v>674</v>
+        <v>837</v>
       </c>
       <c r="C18">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="D18">
-        <v>3.29</v>
+        <v>3.57</v>
       </c>
       <c r="E18">
         <v>0.5</v>
@@ -1663,7 +1663,7 @@
         <v>23.56</v>
       </c>
       <c r="G18">
-        <v>197</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
         <v>0.5</v>
@@ -1688,7 +1688,7 @@
         <v>0.5</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1698,13 +1698,13 @@
         </is>
       </c>
       <c r="B20">
-        <v>162</v>
+        <v>212</v>
       </c>
       <c r="C20">
-        <v>3.74</v>
+        <v>3.64</v>
       </c>
       <c r="D20">
-        <v>7.21</v>
+        <v>6.36</v>
       </c>
       <c r="E20">
         <v>0.5</v>
@@ -1713,7 +1713,7 @@
         <v>32.23</v>
       </c>
       <c r="G20">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
@@ -1738,7 +1738,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>822</v>
+        <v>699</v>
       </c>
     </row>
     <row r="22">
@@ -1748,22 +1748,22 @@
         </is>
       </c>
       <c r="B22">
-        <v>1230</v>
+        <v>1580</v>
       </c>
       <c r="C22">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="D22">
-        <v>4.06</v>
+        <v>5.46</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>49.81</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G22">
-        <v>353</v>
+        <v>468</v>
       </c>
     </row>
     <row r="23">
@@ -1773,22 +1773,22 @@
         </is>
       </c>
       <c r="B23">
-        <v>243</v>
+        <v>334</v>
       </c>
       <c r="C23">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="D23">
-        <v>2.43</v>
+        <v>3.45</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>12.51</v>
+        <v>23.05</v>
       </c>
       <c r="G23">
-        <v>95</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="B24">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="C24">
-        <v>1.08</v>
+        <v>1.37</v>
       </c>
       <c r="D24">
-        <v>2.55</v>
+        <v>3.27</v>
       </c>
       <c r="E24">
         <v>0.5</v>
       </c>
       <c r="F24">
-        <v>18.73</v>
+        <v>22.14</v>
       </c>
       <c r="G24">
-        <v>96</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
@@ -1823,13 +1823,13 @@
         </is>
       </c>
       <c r="B25">
-        <v>154</v>
+        <v>217</v>
       </c>
       <c r="C25">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="D25">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="E25">
         <v>0.5</v>
@@ -1838,7 +1838,7 @@
         <v>12.95</v>
       </c>
       <c r="G25">
-        <v>82</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26">
@@ -1848,22 +1848,22 @@
         </is>
       </c>
       <c r="B26">
-        <v>308</v>
+        <v>474</v>
       </c>
       <c r="C26">
-        <v>1.41</v>
+        <v>1.71</v>
       </c>
       <c r="D26">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="E26">
         <v>0.5</v>
       </c>
       <c r="F26">
-        <v>22</v>
+        <v>23.95</v>
       </c>
       <c r="G26">
-        <v>119</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27">
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="B27">
-        <v>17937</v>
+        <v>26363</v>
       </c>
       <c r="C27">
-        <v>3.14</v>
+        <v>3.74</v>
       </c>
       <c r="D27">
-        <v>6.52</v>
+        <v>6.71</v>
       </c>
       <c r="E27">
         <v>0.5</v>
       </c>
       <c r="F27">
-        <v>72.42</v>
+        <v>81.17</v>
       </c>
       <c r="G27">
-        <v>3510</v>
+        <v>4903</v>
       </c>
     </row>
     <row r="28">
@@ -1898,22 +1898,22 @@
         </is>
       </c>
       <c r="B28">
-        <v>8872</v>
+        <v>12341</v>
       </c>
       <c r="C28">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="D28">
-        <v>5.31</v>
+        <v>4.75</v>
       </c>
       <c r="E28">
         <v>0.5</v>
       </c>
       <c r="F28">
-        <v>52.18</v>
+        <v>53.89</v>
       </c>
       <c r="G28">
-        <v>2372</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="29">
@@ -1923,22 +1923,22 @@
         </is>
       </c>
       <c r="B29">
-        <v>1719</v>
+        <v>2480</v>
       </c>
       <c r="C29">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="D29">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="E29">
         <v>0.5</v>
       </c>
       <c r="F29">
-        <v>45.66</v>
+        <v>52.54</v>
       </c>
       <c r="G29">
-        <v>517</v>
+        <v>702</v>
       </c>
     </row>
     <row r="30">
@@ -1973,22 +1973,22 @@
         </is>
       </c>
       <c r="B31">
-        <v>8210</v>
+        <v>11985</v>
       </c>
       <c r="C31">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="D31">
-        <v>4.12</v>
+        <v>4.29</v>
       </c>
       <c r="E31">
         <v>0.5</v>
       </c>
       <c r="F31">
-        <v>58.91</v>
+        <v>59.63</v>
       </c>
       <c r="G31">
-        <v>2393</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="32">
@@ -1998,22 +1998,22 @@
         </is>
       </c>
       <c r="B32">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="D32">
-        <v>2.22</v>
+        <v>3.78</v>
       </c>
       <c r="E32">
         <v>0.5</v>
       </c>
       <c r="F32">
-        <v>11.78</v>
+        <v>19.74</v>
       </c>
       <c r="G32">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
@@ -2023,22 +2023,22 @@
         </is>
       </c>
       <c r="B33">
-        <v>5072</v>
+        <v>7071</v>
       </c>
       <c r="C33">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="D33">
-        <v>3.85</v>
+        <v>5.83</v>
       </c>
       <c r="E33">
         <v>0.5</v>
       </c>
       <c r="F33">
-        <v>46.59</v>
+        <v>146.1</v>
       </c>
       <c r="G33">
-        <v>1335</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="34">
@@ -2048,22 +2048,22 @@
         </is>
       </c>
       <c r="B34">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C34">
-        <v>4.58</v>
+        <v>3.38</v>
       </c>
       <c r="D34">
-        <v>7.85</v>
+        <v>5.11</v>
       </c>
       <c r="E34">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="F34">
-        <v>22.83</v>
+        <v>19.48</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -2120,22 +2120,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>290262</v>
+        <v>404780</v>
       </c>
       <c r="C2">
-        <v>11.35</v>
+        <v>13.69</v>
       </c>
       <c r="D2">
-        <v>14.75</v>
+        <v>14.72</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>215.4</v>
+        <v>229.48</v>
       </c>
       <c r="G2">
-        <v>17050</v>
+        <v>22167</v>
       </c>
     </row>
     <row r="3">
@@ -2145,22 +2145,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>28608</v>
+        <v>40711</v>
       </c>
       <c r="C3">
-        <v>2.57</v>
+        <v>2.98</v>
       </c>
       <c r="D3">
-        <v>5.38</v>
+        <v>6.07</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>98.56999999999999</v>
+        <v>162.05</v>
       </c>
       <c r="G3">
-        <v>6507</v>
+        <v>9078</v>
       </c>
     </row>
     <row r="4">
@@ -2170,22 +2170,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>32143</v>
+        <v>42958</v>
       </c>
       <c r="C4">
-        <v>4.32</v>
+        <v>4.74</v>
       </c>
       <c r="D4">
-        <v>10.32</v>
+        <v>9.15</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>111.43</v>
+        <v>112.76</v>
       </c>
       <c r="G4">
-        <v>4718</v>
+        <v>6181</v>
       </c>
     </row>
   </sheetData>
@@ -2242,22 +2242,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>290262</v>
+        <v>404780</v>
       </c>
       <c r="C2">
-        <v>11.35</v>
+        <v>13.69</v>
       </c>
       <c r="D2">
-        <v>14.75</v>
+        <v>14.72</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>215.4</v>
+        <v>229.48</v>
       </c>
       <c r="G2">
-        <v>17050</v>
+        <v>22167</v>
       </c>
     </row>
     <row r="3">
@@ -2282,7 +2282,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>822</v>
+        <v>699</v>
       </c>
     </row>
     <row r="4">
@@ -2292,22 +2292,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>28608</v>
+        <v>40711</v>
       </c>
       <c r="C4">
-        <v>2.57</v>
+        <v>2.98</v>
       </c>
       <c r="D4">
-        <v>5.38</v>
+        <v>6.07</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>98.56999999999999</v>
+        <v>162.05</v>
       </c>
       <c r="G4">
-        <v>6507</v>
+        <v>9078</v>
       </c>
     </row>
     <row r="5">
@@ -2317,22 +2317,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>32143</v>
+        <v>42958</v>
       </c>
       <c r="C5">
-        <v>4.32</v>
+        <v>4.74</v>
       </c>
       <c r="D5">
-        <v>10.32</v>
+        <v>9.15</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>111.43</v>
+        <v>112.76</v>
       </c>
       <c r="G5">
-        <v>4718</v>
+        <v>6181</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -401,19 +401,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>267</v>
+        <v>346</v>
       </c>
       <c r="C2">
-        <v>2.21</v>
+        <v>2.87</v>
       </c>
       <c r="D2">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>16.79</v>
+        <v>21.51</v>
       </c>
       <c r="G2">
         <v>81</v>
@@ -422,775 +422,975 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Practitioner - General Practitioner</t>
+          <t>Assistant Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>2122</v>
+        <v>581</v>
       </c>
       <c r="C3">
-        <v>3.18</v>
+        <v>2.78</v>
       </c>
       <c r="D3">
-        <v>6.24</v>
+        <v>5.43</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>79.40000000000001</v>
+        <v>31.56</v>
       </c>
       <c r="G3">
-        <v>452</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Practitioner - Nurse</t>
+          <t>Associate Practitioner - General Practitioner</t>
         </is>
       </c>
       <c r="B4">
-        <v>1950</v>
+        <v>2996</v>
       </c>
       <c r="C4">
-        <v>2.02</v>
+        <v>4.49</v>
       </c>
       <c r="D4">
-        <v>4.19</v>
+        <v>10.74</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>44.54</v>
+        <v>150.86</v>
       </c>
       <c r="G4">
-        <v>627</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Specialist</t>
+          <t>Associate Practitioner - Nurse</t>
         </is>
       </c>
       <c r="B5">
-        <v>192</v>
+        <v>2457</v>
       </c>
       <c r="C5">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="D5">
-        <v>5.27</v>
+        <v>5.57</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>34.6</v>
+        <v>56.82</v>
       </c>
       <c r="G5">
-        <v>62</v>
+        <v>627</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist</t>
+          <t>Associate Specialist</t>
         </is>
       </c>
       <c r="B6">
-        <v>111</v>
+        <v>204</v>
       </c>
       <c r="C6">
-        <v>1.08</v>
+        <v>2.25</v>
       </c>
       <c r="D6">
-        <v>1.17</v>
+        <v>5.76</v>
       </c>
       <c r="E6">
         <v>0.5</v>
       </c>
       <c r="F6">
-        <v>5.5</v>
+        <v>38.45</v>
       </c>
       <c r="G6">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Clinical Psychologist</t>
+          <t>Chiropodist/Podiatrist</t>
         </is>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>119</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="D7">
-        <v>0.71</v>
+        <v>1.18</v>
       </c>
       <c r="E7">
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Community Mental Health Nurse</t>
+          <t>Clinical Assistant</t>
         </is>
       </c>
       <c r="B8">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="C8">
-        <v>2.22</v>
+        <v>2.57</v>
       </c>
       <c r="D8">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>14.05</v>
+        <v>25.48</v>
       </c>
       <c r="G8">
-        <v>29</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Community Nurse</t>
+          <t>Clinical Psychologist</t>
         </is>
       </c>
       <c r="B9">
-        <v>15343</v>
+        <v>8</v>
       </c>
       <c r="C9">
-        <v>2.69</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>5.93</v>
+        <v>0.71</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>162.05</v>
+        <v>2</v>
       </c>
       <c r="G9">
-        <v>3742</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Community Practitioner</t>
+          <t>Community Mental Health Nurse</t>
         </is>
       </c>
       <c r="B10">
-        <v>43287</v>
+        <v>93</v>
       </c>
       <c r="C10">
-        <v>2.94</v>
+        <v>2.29</v>
       </c>
       <c r="D10">
-        <v>5.46</v>
+        <v>3.9</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>186.45</v>
+        <v>14.05</v>
       </c>
       <c r="G10">
-        <v>9496</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Community Nurse</t>
         </is>
       </c>
       <c r="B11">
-        <v>2046</v>
+        <v>18702</v>
       </c>
       <c r="C11">
-        <v>2.87</v>
+        <v>3.27</v>
       </c>
       <c r="D11">
-        <v>5.91</v>
+        <v>7.98</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>45.66</v>
+        <v>182.62</v>
       </c>
       <c r="G11">
-        <v>465</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Counsellor</t>
+          <t>Community Practitioner</t>
         </is>
       </c>
       <c r="B12">
-        <v>128</v>
+        <v>49421</v>
       </c>
       <c r="C12">
-        <v>2.66</v>
+        <v>3.36</v>
       </c>
       <c r="D12">
-        <v>3.21</v>
+        <v>6.63</v>
       </c>
       <c r="E12">
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>15.01</v>
+        <v>197.92</v>
       </c>
       <c r="G12">
-        <v>28</v>
+        <v>9496</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dietitian</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B13">
-        <v>79</v>
+        <v>2232</v>
       </c>
       <c r="C13">
-        <v>0.87</v>
+        <v>3.13</v>
       </c>
       <c r="D13">
-        <v>1.46</v>
+        <v>6.95</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>8.82</v>
+        <v>54.4</v>
       </c>
       <c r="G13">
-        <v>55</v>
+        <v>465</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>Counsellor</t>
         </is>
       </c>
       <c r="B14">
-        <v>11921</v>
+        <v>152</v>
       </c>
       <c r="C14">
-        <v>1.85</v>
+        <v>3.16</v>
       </c>
       <c r="D14">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>71.27</v>
+        <v>19.51</v>
       </c>
       <c r="G14">
-        <v>4204</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Dietitian</t>
         </is>
       </c>
       <c r="B15">
-        <v>303981</v>
+        <v>81</v>
       </c>
       <c r="C15">
-        <v>10.5</v>
+        <v>0.89</v>
       </c>
       <c r="D15">
-        <v>12.21</v>
+        <v>1.74</v>
       </c>
       <c r="E15">
         <v>0.5</v>
       </c>
       <c r="F15">
-        <v>166.11</v>
+        <v>8.91</v>
       </c>
       <c r="G15">
-        <v>21488</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="B16">
-        <v>37858</v>
+        <v>14349</v>
       </c>
       <c r="C16">
-        <v>5.14</v>
+        <v>2.23</v>
       </c>
       <c r="D16">
-        <v>9.69</v>
+        <v>5.12</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>112.76</v>
+        <v>115.81</v>
       </c>
       <c r="G16">
-        <v>5023</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="B17">
-        <v>4765</v>
+        <v>401172</v>
       </c>
       <c r="C17">
-        <v>2.43</v>
+        <v>13.85</v>
       </c>
       <c r="D17">
-        <v>5.19</v>
+        <v>17.77</v>
       </c>
       <c r="E17">
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>69.56999999999999</v>
+        <v>249.91</v>
       </c>
       <c r="G17">
-        <v>1302</v>
+        <v>21488</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="B18">
-        <v>837</v>
+        <v>46310</v>
       </c>
       <c r="C18">
-        <v>2.11</v>
+        <v>6.28</v>
       </c>
       <c r="D18">
-        <v>3.57</v>
+        <v>13.84</v>
       </c>
       <c r="E18">
         <v>0.5</v>
       </c>
       <c r="F18">
-        <v>23.56</v>
+        <v>197.74</v>
       </c>
       <c r="G18">
-        <v>263</v>
+        <v>5023</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Healthcare Assistant</t>
         </is>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>29189</v>
       </c>
       <c r="C19">
-        <v>0.5</v>
+        <v>2.59</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>0.5</v>
+        <v>84.52</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>7339</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Modern Matron</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="B20">
-        <v>212</v>
+        <v>6025</v>
       </c>
       <c r="C20">
-        <v>3.64</v>
+        <v>3.08</v>
       </c>
       <c r="D20">
-        <v>6.36</v>
+        <v>7.96</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>32.23</v>
+        <v>165.23</v>
       </c>
       <c r="G20">
-        <v>42</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nurse Consultant</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="B21">
-        <v>1580</v>
+        <v>873</v>
       </c>
       <c r="C21">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="D21">
-        <v>5.46</v>
+        <v>3.78</v>
       </c>
       <c r="E21">
         <v>0.5</v>
       </c>
       <c r="F21">
-        <v>77.04000000000001</v>
+        <v>23.56</v>
       </c>
       <c r="G21">
-        <v>468</v>
+        <v>263</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Other Community Health Service</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B22">
-        <v>334</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>1.94</v>
+        <v>0.5</v>
       </c>
       <c r="D22">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>23.05</v>
+        <v>0.5</v>
       </c>
       <c r="G22">
-        <v>121</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="B23">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="C23">
-        <v>1.37</v>
+        <v>3.85</v>
       </c>
       <c r="D23">
-        <v>3.27</v>
+        <v>6.71</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>22.14</v>
+        <v>32.23</v>
       </c>
       <c r="G23">
-        <v>116</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Paramedic Specialist Practitioner</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="B24">
-        <v>217</v>
+        <v>1916</v>
       </c>
       <c r="C24">
-        <v>1.55</v>
+        <v>2.6</v>
       </c>
       <c r="D24">
-        <v>2.52</v>
+        <v>6.41</v>
       </c>
       <c r="E24">
         <v>0.5</v>
       </c>
       <c r="F24">
-        <v>12.95</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G24">
-        <v>110</v>
+        <v>468</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Physiotherapist</t>
+          <t>Nurse Manager</t>
         </is>
       </c>
       <c r="B25">
-        <v>474</v>
+        <v>2695</v>
       </c>
       <c r="C25">
-        <v>1.71</v>
+        <v>2.77</v>
       </c>
       <c r="D25">
-        <v>2.81</v>
+        <v>6.68</v>
       </c>
       <c r="E25">
         <v>0.5</v>
       </c>
       <c r="F25">
-        <v>23.95</v>
+        <v>84.94</v>
       </c>
       <c r="G25">
-        <v>178</v>
+        <v>616</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Salaried General Practitioner</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="B26">
-        <v>26363</v>
+        <v>357</v>
       </c>
       <c r="C26">
-        <v>3.74</v>
+        <v>2.08</v>
       </c>
       <c r="D26">
-        <v>6.71</v>
+        <v>3.61</v>
       </c>
       <c r="E26">
         <v>0.5</v>
       </c>
       <c r="F26">
-        <v>81.17</v>
+        <v>24.82</v>
       </c>
       <c r="G26">
-        <v>4903</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sessional GP</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B27">
-        <v>12341</v>
+        <v>255</v>
       </c>
       <c r="C27">
-        <v>2.44</v>
+        <v>1.66</v>
       </c>
       <c r="D27">
-        <v>4.75</v>
+        <v>4.07</v>
       </c>
       <c r="E27">
         <v>0.5</v>
       </c>
       <c r="F27">
-        <v>53.89</v>
+        <v>22.14</v>
       </c>
       <c r="G27">
-        <v>3311</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sister/Charge Nurse</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="B28">
-        <v>2480</v>
+        <v>271</v>
       </c>
       <c r="C28">
-        <v>2.24</v>
+        <v>1.94</v>
       </c>
       <c r="D28">
-        <v>4.62</v>
+        <v>4.9</v>
       </c>
       <c r="E28">
         <v>0.5</v>
       </c>
       <c r="F28">
-        <v>52.54</v>
+        <v>44.04</v>
       </c>
       <c r="G28">
-        <v>702</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Pharmacist</t>
         </is>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>6001</v>
       </c>
       <c r="C29">
-        <v>3.53</v>
+        <v>1.72</v>
       </c>
       <c r="D29">
-        <v>1.92</v>
+        <v>3.44</v>
       </c>
       <c r="E29">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
       <c r="F29">
-        <v>4.36</v>
+        <v>36.89</v>
       </c>
       <c r="G29">
-        <v>2</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Specialist Nurse Practitioner</t>
+          <t>Phlebotomist</t>
         </is>
       </c>
       <c r="B30">
-        <v>11985</v>
+        <v>6611</v>
       </c>
       <c r="C30">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="D30">
-        <v>4.29</v>
+        <v>3.98</v>
       </c>
       <c r="E30">
         <v>0.5</v>
       </c>
       <c r="F30">
-        <v>59.63</v>
+        <v>48.63</v>
       </c>
       <c r="G30">
-        <v>3450</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Specialist Practitioner</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B31">
-        <v>135</v>
+        <v>22</v>
       </c>
       <c r="C31">
-        <v>2.13</v>
+        <v>1.4</v>
       </c>
       <c r="D31">
-        <v>3.78</v>
+        <v>1.37</v>
       </c>
       <c r="E31">
         <v>0.5</v>
       </c>
       <c r="F31">
-        <v>19.74</v>
+        <v>4.5</v>
       </c>
       <c r="G31">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Staff Nurse</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="B32">
-        <v>7071</v>
+        <v>493</v>
       </c>
       <c r="C32">
-        <v>2.48</v>
+        <v>1.78</v>
       </c>
       <c r="D32">
-        <v>5.83</v>
+        <v>2.85</v>
       </c>
       <c r="E32">
         <v>0.5</v>
       </c>
       <c r="F32">
-        <v>146.1</v>
+        <v>23.95</v>
       </c>
       <c r="G32">
-        <v>1845</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Radiographer</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="C33">
+        <v>2.43</v>
+      </c>
+      <c r="D33">
+        <v>1.71</v>
+      </c>
+      <c r="E33">
+        <v>0.5</v>
+      </c>
+      <c r="F33">
+        <v>5.5</v>
+      </c>
+      <c r="G33">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Salaried General Practitioner</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>33882</v>
+      </c>
+      <c r="C34">
+        <v>4.81</v>
+      </c>
+      <c r="D34">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="E34">
+        <v>0.5</v>
+      </c>
+      <c r="F34">
+        <v>143.06</v>
+      </c>
+      <c r="G34">
+        <v>4903</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Sessional GP</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>15321</v>
+      </c>
+      <c r="C35">
+        <v>3.03</v>
+      </c>
+      <c r="D35">
+        <v>6.29</v>
+      </c>
+      <c r="E35">
+        <v>0.5</v>
+      </c>
+      <c r="F35">
+        <v>76.05</v>
+      </c>
+      <c r="G35">
+        <v>3311</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sister/Charge Nurse</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>2965</v>
+      </c>
+      <c r="C36">
+        <v>2.68</v>
+      </c>
+      <c r="D36">
+        <v>5.52</v>
+      </c>
+      <c r="E36">
+        <v>0.5</v>
+      </c>
+      <c r="F36">
+        <v>60.04</v>
+      </c>
+      <c r="G36">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>9</v>
+      </c>
+      <c r="C37">
+        <v>4.53</v>
+      </c>
+      <c r="D37">
+        <v>2.94</v>
+      </c>
+      <c r="E37">
+        <v>1.65</v>
+      </c>
+      <c r="F37">
+        <v>5.81</v>
+      </c>
+      <c r="G37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Specialist Nurse Practitioner</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>14765</v>
+      </c>
+      <c r="C38">
+        <v>2.83</v>
+      </c>
+      <c r="D38">
+        <v>5.62</v>
+      </c>
+      <c r="E38">
+        <v>0.5</v>
+      </c>
+      <c r="F38">
+        <v>102.63</v>
+      </c>
+      <c r="G38">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>140</v>
+      </c>
+      <c r="C39">
+        <v>2.21</v>
+      </c>
+      <c r="D39">
+        <v>3.76</v>
+      </c>
+      <c r="E39">
+        <v>0.5</v>
+      </c>
+      <c r="F39">
+        <v>19.74</v>
+      </c>
+      <c r="G39">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Staff Nurse</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>8286</v>
+      </c>
+      <c r="C40">
+        <v>2.9</v>
+      </c>
+      <c r="D40">
+        <v>6.99</v>
+      </c>
+      <c r="E40">
+        <v>0.5</v>
+      </c>
+      <c r="F40">
+        <v>154.22</v>
+      </c>
+      <c r="G40">
+        <v>1845</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>Therapist</t>
         </is>
       </c>
-      <c r="B33">
+      <c r="B41">
         <v>51</v>
       </c>
-      <c r="C33">
+      <c r="C41">
         <v>3.38</v>
       </c>
-      <c r="D33">
+      <c r="D41">
         <v>5.11</v>
       </c>
-      <c r="E33">
-        <v>0.5</v>
-      </c>
-      <c r="F33">
+      <c r="E41">
+        <v>0.5</v>
+      </c>
+      <c r="F41">
         <v>19.48</v>
       </c>
-      <c r="G33">
+      <c r="G41">
         <v>13</v>
       </c>
     </row>
@@ -1201,7 +1401,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1240,6 +1440,11 @@
           <t>num_subjects_visited</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>num_non_users</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1248,822 +1453,1649 @@
         </is>
       </c>
       <c r="B2">
-        <v>267</v>
+        <v>346</v>
       </c>
       <c r="C2">
-        <v>2.21</v>
+        <v>2.87</v>
       </c>
       <c r="D2">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>16.79</v>
+        <v>21.51</v>
       </c>
       <c r="G2">
         <v>81</v>
       </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Practitioner - General Practitioner</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="B3">
-        <v>2122</v>
+        <v>79</v>
       </c>
       <c r="C3">
-        <v>3.18</v>
+        <v>1.42</v>
       </c>
       <c r="D3">
-        <v>6.24</v>
+        <v>9.65</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>79.40000000000001</v>
+        <v>57.07</v>
       </c>
       <c r="G3">
-        <v>452</v>
+        <v>35</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Practitioner - Nurse</t>
+          <t>Assistant Practitioner</t>
         </is>
       </c>
       <c r="B4">
-        <v>1950</v>
+        <v>581</v>
       </c>
       <c r="C4">
-        <v>2.02</v>
+        <v>2.78</v>
       </c>
       <c r="D4">
-        <v>4.19</v>
+        <v>5.43</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>44.54</v>
+        <v>31.56</v>
       </c>
       <c r="G4">
-        <v>627</v>
+        <v>134</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Specialist</t>
+          <t>Associate Practitioner - General Practitioner</t>
         </is>
       </c>
       <c r="B5">
-        <v>192</v>
+        <v>2996</v>
       </c>
       <c r="C5">
-        <v>2.12</v>
+        <v>4.49</v>
       </c>
       <c r="D5">
-        <v>5.27</v>
+        <v>10.74</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>34.6</v>
+        <v>150.86</v>
       </c>
       <c r="G5">
-        <v>62</v>
+        <v>452</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist</t>
+          <t>Associate Practitioner - Nurse</t>
         </is>
       </c>
       <c r="B6">
-        <v>111</v>
+        <v>2457</v>
       </c>
       <c r="C6">
-        <v>1.08</v>
+        <v>2.54</v>
       </c>
       <c r="D6">
-        <v>1.17</v>
+        <v>5.57</v>
       </c>
       <c r="E6">
         <v>0.5</v>
       </c>
       <c r="F6">
-        <v>5.5</v>
+        <v>56.82</v>
       </c>
       <c r="G6">
-        <v>60</v>
+        <v>627</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Clinical Psychologist</t>
+          <t>Associate Specialist</t>
         </is>
       </c>
       <c r="B7">
-        <v>8</v>
+        <v>204</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="D7">
-        <v>0.71</v>
+        <v>5.76</v>
       </c>
       <c r="E7">
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>38.45</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>62</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Community Mental Health Nurse</t>
+          <t>Chiropodist/Podiatrist</t>
         </is>
       </c>
       <c r="B8">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="C8">
-        <v>2.22</v>
+        <v>1.16</v>
       </c>
       <c r="D8">
-        <v>3.9</v>
+        <v>1.18</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>14.05</v>
+        <v>5.5</v>
       </c>
       <c r="G8">
-        <v>29</v>
+        <v>60</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Community Nurse</t>
+          <t>Clerical Worker</t>
         </is>
       </c>
       <c r="B9">
-        <v>15343</v>
+        <v>52837</v>
       </c>
       <c r="C9">
-        <v>2.69</v>
+        <v>4.56</v>
       </c>
       <c r="D9">
-        <v>5.93</v>
+        <v>10.58</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>162.05</v>
+        <v>326.8</v>
       </c>
       <c r="G9">
-        <v>3742</v>
+        <v>8053</v>
+      </c>
+      <c r="H9">
+        <v>120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Community Practitioner</t>
+          <t>Clinical Assistant</t>
         </is>
       </c>
       <c r="B10">
-        <v>43287</v>
+        <v>580</v>
       </c>
       <c r="C10">
-        <v>2.94</v>
+        <v>2.57</v>
       </c>
       <c r="D10">
-        <v>5.46</v>
+        <v>3.92</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>186.45</v>
+        <v>25.48</v>
       </c>
       <c r="G10">
-        <v>9496</v>
+        <v>146</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Clinical Coder</t>
         </is>
       </c>
       <c r="B11">
-        <v>2046</v>
+        <v>4416</v>
       </c>
       <c r="C11">
-        <v>2.87</v>
+        <v>3.46</v>
       </c>
       <c r="D11">
-        <v>5.91</v>
+        <v>7.57</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>45.66</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="G11">
-        <v>465</v>
+        <v>911</v>
+      </c>
+      <c r="H11">
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Counsellor</t>
+          <t>Clinical Psychologist</t>
         </is>
       </c>
       <c r="B12">
-        <v>128</v>
+        <v>8</v>
       </c>
       <c r="C12">
-        <v>2.66</v>
+        <v>1</v>
       </c>
       <c r="D12">
-        <v>3.21</v>
+        <v>0.71</v>
       </c>
       <c r="E12">
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>15.01</v>
+        <v>2</v>
       </c>
       <c r="G12">
-        <v>28</v>
+        <v>4</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dietitian</t>
+          <t>Community Administrator</t>
         </is>
       </c>
       <c r="B13">
-        <v>79</v>
+        <v>25691</v>
       </c>
       <c r="C13">
-        <v>0.87</v>
+        <v>6.17</v>
       </c>
       <c r="D13">
-        <v>1.46</v>
+        <v>18.26</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>8.82</v>
+        <v>738.38</v>
       </c>
       <c r="G13">
-        <v>55</v>
+        <v>2828</v>
+      </c>
+      <c r="H13">
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>Community Mental Health Nurse</t>
         </is>
       </c>
       <c r="B14">
-        <v>11921</v>
+        <v>93</v>
       </c>
       <c r="C14">
-        <v>1.85</v>
+        <v>2.29</v>
       </c>
       <c r="D14">
-        <v>3.76</v>
+        <v>3.9</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>71.27</v>
+        <v>14.05</v>
       </c>
       <c r="G14">
-        <v>4204</v>
+        <v>29</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Community Nurse</t>
         </is>
       </c>
       <c r="B15">
-        <v>303981</v>
+        <v>18702</v>
       </c>
       <c r="C15">
-        <v>10.5</v>
+        <v>3.27</v>
       </c>
       <c r="D15">
-        <v>12.21</v>
+        <v>7.98</v>
       </c>
       <c r="E15">
         <v>0.5</v>
       </c>
       <c r="F15">
-        <v>166.11</v>
+        <v>182.62</v>
       </c>
       <c r="G15">
-        <v>21488</v>
+        <v>3742</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>Community Practitioner</t>
         </is>
       </c>
       <c r="B16">
-        <v>37858</v>
+        <v>49421</v>
       </c>
       <c r="C16">
-        <v>5.14</v>
+        <v>3.36</v>
       </c>
       <c r="D16">
-        <v>9.69</v>
+        <v>6.63</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>112.76</v>
+        <v>197.92</v>
       </c>
       <c r="G16">
-        <v>5023</v>
+        <v>9496</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B17">
-        <v>4765</v>
+        <v>2232</v>
       </c>
       <c r="C17">
-        <v>2.43</v>
+        <v>3.13</v>
       </c>
       <c r="D17">
-        <v>5.19</v>
+        <v>6.95</v>
       </c>
       <c r="E17">
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>69.56999999999999</v>
+        <v>54.4</v>
       </c>
       <c r="G17">
-        <v>1302</v>
+        <v>465</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Counsellor</t>
         </is>
       </c>
       <c r="B18">
-        <v>837</v>
+        <v>152</v>
       </c>
       <c r="C18">
-        <v>2.11</v>
+        <v>3.16</v>
       </c>
       <c r="D18">
-        <v>3.57</v>
+        <v>4.2</v>
       </c>
       <c r="E18">
         <v>0.5</v>
       </c>
       <c r="F18">
-        <v>23.56</v>
+        <v>19.51</v>
       </c>
       <c r="G18">
-        <v>263</v>
+        <v>28</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Desktop Support Administrator</t>
         </is>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>24519</v>
       </c>
       <c r="C19">
-        <v>0.5</v>
+        <v>7.19</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>11.73</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>0.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>2486</v>
+      </c>
+      <c r="H19">
+        <v>68</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Modern Matron</t>
+          <t>Desktop Support Technician</t>
         </is>
       </c>
       <c r="B20">
-        <v>212</v>
+        <v>1098</v>
       </c>
       <c r="C20">
-        <v>3.64</v>
+        <v>7.96</v>
       </c>
       <c r="D20">
-        <v>6.36</v>
+        <v>11.3</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>32.23</v>
+        <v>52.18</v>
       </c>
       <c r="G20">
-        <v>42</v>
+        <v>100</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Not Clinically Relevant</t>
+          <t>Dietitian</t>
         </is>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>8.91</v>
       </c>
       <c r="G21">
-        <v>699</v>
+        <v>55</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Nurse Consultant</t>
+          <t>Dispenser</t>
         </is>
       </c>
       <c r="B22">
-        <v>1580</v>
+        <v>5766</v>
       </c>
       <c r="C22">
-        <v>2.14</v>
+        <v>4.22</v>
       </c>
       <c r="D22">
-        <v>5.46</v>
+        <v>8.98</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>77.04000000000001</v>
+        <v>133.63</v>
       </c>
       <c r="G22">
-        <v>468</v>
+        <v>903</v>
+      </c>
+      <c r="H22">
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Other Community Health Service</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="B23">
-        <v>334</v>
+        <v>14349</v>
       </c>
       <c r="C23">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="D23">
-        <v>3.45</v>
+        <v>5.12</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>23.05</v>
+        <v>115.81</v>
       </c>
       <c r="G23">
-        <v>121</v>
+        <v>4204</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="B24">
-        <v>211</v>
+        <v>401172</v>
       </c>
       <c r="C24">
-        <v>1.37</v>
+        <v>13.85</v>
       </c>
       <c r="D24">
-        <v>3.27</v>
+        <v>17.77</v>
       </c>
       <c r="E24">
         <v>0.5</v>
       </c>
       <c r="F24">
-        <v>22.14</v>
+        <v>249.91</v>
       </c>
       <c r="G24">
-        <v>116</v>
+        <v>21488</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Paramedic Specialist Practitioner</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="B25">
-        <v>217</v>
+        <v>46310</v>
       </c>
       <c r="C25">
-        <v>1.55</v>
+        <v>6.28</v>
       </c>
       <c r="D25">
-        <v>2.52</v>
+        <v>13.84</v>
       </c>
       <c r="E25">
         <v>0.5</v>
       </c>
       <c r="F25">
-        <v>12.95</v>
+        <v>197.74</v>
       </c>
       <c r="G25">
-        <v>110</v>
+        <v>5023</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Physiotherapist</t>
+          <t>Health Records Administrator</t>
         </is>
       </c>
       <c r="B26">
-        <v>474</v>
+        <v>541</v>
       </c>
       <c r="C26">
-        <v>1.71</v>
+        <v>1.98</v>
       </c>
       <c r="D26">
-        <v>2.81</v>
+        <v>3.73</v>
       </c>
       <c r="E26">
         <v>0.5</v>
       </c>
       <c r="F26">
-        <v>23.95</v>
+        <v>29.22</v>
       </c>
       <c r="G26">
-        <v>178</v>
+        <v>181</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Salaried General Practitioner</t>
+          <t>Healthcare Assistant</t>
         </is>
       </c>
       <c r="B27">
-        <v>26363</v>
+        <v>29189</v>
       </c>
       <c r="C27">
-        <v>3.74</v>
+        <v>2.59</v>
       </c>
       <c r="D27">
-        <v>6.71</v>
+        <v>4.61</v>
       </c>
       <c r="E27">
         <v>0.5</v>
       </c>
       <c r="F27">
-        <v>81.17</v>
+        <v>84.52</v>
       </c>
       <c r="G27">
-        <v>4903</v>
+        <v>7339</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sessional GP</t>
+          <t>Helpdesk Administrator</t>
         </is>
       </c>
       <c r="B28">
-        <v>12341</v>
+        <v>1225</v>
       </c>
       <c r="C28">
-        <v>2.44</v>
+        <v>5.14</v>
       </c>
       <c r="D28">
-        <v>4.75</v>
+        <v>13.52</v>
       </c>
       <c r="E28">
         <v>0.5</v>
       </c>
       <c r="F28">
-        <v>53.89</v>
+        <v>115.81</v>
       </c>
       <c r="G28">
-        <v>3311</v>
+        <v>165</v>
+      </c>
+      <c r="H28">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sister/Charge Nurse</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="B29">
-        <v>2480</v>
+        <v>6025</v>
       </c>
       <c r="C29">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="D29">
-        <v>4.62</v>
+        <v>7.96</v>
       </c>
       <c r="E29">
         <v>0.5</v>
       </c>
       <c r="F29">
-        <v>52.54</v>
+        <v>165.23</v>
       </c>
       <c r="G29">
-        <v>702</v>
+        <v>1302</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="B30">
-        <v>7</v>
+        <v>85436</v>
       </c>
       <c r="C30">
-        <v>3.53</v>
+        <v>5.51</v>
       </c>
       <c r="D30">
-        <v>1.92</v>
+        <v>11.02</v>
       </c>
       <c r="E30">
-        <v>1.65</v>
+        <v>0.5</v>
       </c>
       <c r="F30">
-        <v>4.36</v>
+        <v>239.44</v>
       </c>
       <c r="G30">
-        <v>2</v>
+        <v>11066</v>
+      </c>
+      <c r="H30">
+        <v>212</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Specialist Nurse Practitioner</t>
+          <t>Medical Records Clerk</t>
         </is>
       </c>
       <c r="B31">
-        <v>11985</v>
+        <v>1011</v>
       </c>
       <c r="C31">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="D31">
-        <v>4.29</v>
+        <v>7.31</v>
       </c>
       <c r="E31">
         <v>0.5</v>
       </c>
       <c r="F31">
-        <v>59.63</v>
+        <v>50.19</v>
       </c>
       <c r="G31">
-        <v>3450</v>
+        <v>195</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Specialist Practitioner</t>
+          <t>Medical Secretary</t>
         </is>
       </c>
       <c r="B32">
-        <v>135</v>
+        <v>15820</v>
       </c>
       <c r="C32">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="D32">
-        <v>3.78</v>
+        <v>6.57</v>
       </c>
       <c r="E32">
         <v>0.5</v>
       </c>
       <c r="F32">
-        <v>19.74</v>
+        <v>118.17</v>
       </c>
       <c r="G32">
-        <v>41</v>
+        <v>4259</v>
+      </c>
+      <c r="H32">
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Staff Nurse</t>
+          <t>Medical Student</t>
         </is>
       </c>
       <c r="B33">
-        <v>7071</v>
+        <v>236</v>
       </c>
       <c r="C33">
-        <v>2.48</v>
+        <v>0.78</v>
       </c>
       <c r="D33">
-        <v>5.83</v>
+        <v>1.42</v>
       </c>
       <c r="E33">
         <v>0.5</v>
       </c>
       <c r="F33">
-        <v>146.1</v>
+        <v>11.41</v>
       </c>
       <c r="G33">
-        <v>1845</v>
+        <v>193</v>
+      </c>
+      <c r="H33">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Medical Technical Officer - Pharmacy</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>873</v>
+      </c>
+      <c r="C34">
+        <v>2.2</v>
+      </c>
+      <c r="D34">
+        <v>3.78</v>
+      </c>
+      <c r="E34">
+        <v>0.5</v>
+      </c>
+      <c r="F34">
+        <v>23.56</v>
+      </c>
+      <c r="G34">
+        <v>263</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Midwife</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>3</v>
+      </c>
+      <c r="C35">
+        <v>0.5</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0.5</v>
+      </c>
+      <c r="F35">
+        <v>0.5</v>
+      </c>
+      <c r="G35">
+        <v>3</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Modern Matron</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>224</v>
+      </c>
+      <c r="C36">
+        <v>3.85</v>
+      </c>
+      <c r="D36">
+        <v>6.71</v>
+      </c>
+      <c r="E36">
+        <v>0.5</v>
+      </c>
+      <c r="F36">
+        <v>32.23</v>
+      </c>
+      <c r="G36">
+        <v>42</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Nurse Consultant</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>1916</v>
+      </c>
+      <c r="C37">
+        <v>2.6</v>
+      </c>
+      <c r="D37">
+        <v>6.41</v>
+      </c>
+      <c r="E37">
+        <v>0.5</v>
+      </c>
+      <c r="F37">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="G37">
+        <v>468</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Nurse Manager</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>2695</v>
+      </c>
+      <c r="C38">
+        <v>2.77</v>
+      </c>
+      <c r="D38">
+        <v>6.68</v>
+      </c>
+      <c r="E38">
+        <v>0.5</v>
+      </c>
+      <c r="F38">
+        <v>84.94</v>
+      </c>
+      <c r="G38">
+        <v>616</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Other Community Health Service</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>357</v>
+      </c>
+      <c r="C39">
+        <v>2.08</v>
+      </c>
+      <c r="D39">
+        <v>3.61</v>
+      </c>
+      <c r="E39">
+        <v>0.5</v>
+      </c>
+      <c r="F39">
+        <v>24.82</v>
+      </c>
+      <c r="G39">
+        <v>121</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Paramedic</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>255</v>
+      </c>
+      <c r="C40">
+        <v>1.66</v>
+      </c>
+      <c r="D40">
+        <v>4.07</v>
+      </c>
+      <c r="E40">
+        <v>0.5</v>
+      </c>
+      <c r="F40">
+        <v>22.14</v>
+      </c>
+      <c r="G40">
+        <v>116</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Paramedic Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>271</v>
+      </c>
+      <c r="C41">
+        <v>1.94</v>
+      </c>
+      <c r="D41">
+        <v>4.9</v>
+      </c>
+      <c r="E41">
+        <v>0.5</v>
+      </c>
+      <c r="F41">
+        <v>44.04</v>
+      </c>
+      <c r="G41">
+        <v>110</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Pharmacist</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>6001</v>
+      </c>
+      <c r="C42">
+        <v>1.72</v>
+      </c>
+      <c r="D42">
+        <v>3.44</v>
+      </c>
+      <c r="E42">
+        <v>0.5</v>
+      </c>
+      <c r="F42">
+        <v>36.89</v>
+      </c>
+      <c r="G42">
+        <v>2412</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Phlebotomist</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>6611</v>
+      </c>
+      <c r="C43">
+        <v>2.27</v>
+      </c>
+      <c r="D43">
+        <v>3.98</v>
+      </c>
+      <c r="E43">
+        <v>0.5</v>
+      </c>
+      <c r="F43">
+        <v>48.63</v>
+      </c>
+      <c r="G43">
+        <v>1865</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Physician Assistant</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>22</v>
+      </c>
+      <c r="C44">
+        <v>1.4</v>
+      </c>
+      <c r="D44">
+        <v>1.37</v>
+      </c>
+      <c r="E44">
+        <v>0.5</v>
+      </c>
+      <c r="F44">
+        <v>4.5</v>
+      </c>
+      <c r="G44">
+        <v>9</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Physiotherapist</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>493</v>
+      </c>
+      <c r="C45">
+        <v>1.78</v>
+      </c>
+      <c r="D45">
+        <v>2.85</v>
+      </c>
+      <c r="E45">
+        <v>0.5</v>
+      </c>
+      <c r="F45">
+        <v>23.95</v>
+      </c>
+      <c r="G45">
+        <v>178</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Radiographer</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>30</v>
+      </c>
+      <c r="C46">
+        <v>2.43</v>
+      </c>
+      <c r="D46">
+        <v>1.71</v>
+      </c>
+      <c r="E46">
+        <v>0.5</v>
+      </c>
+      <c r="F46">
+        <v>5.5</v>
+      </c>
+      <c r="G46">
+        <v>7</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Receptionist</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>101721</v>
+      </c>
+      <c r="C47">
+        <v>6.07</v>
+      </c>
+      <c r="D47">
+        <v>12.54</v>
+      </c>
+      <c r="E47">
+        <v>0.5</v>
+      </c>
+      <c r="F47">
+        <v>426.29</v>
+      </c>
+      <c r="G47">
+        <v>11764</v>
+      </c>
+      <c r="H47">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Salaried General Practitioner</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>33882</v>
+      </c>
+      <c r="C48">
+        <v>4.81</v>
+      </c>
+      <c r="D48">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="E48">
+        <v>0.5</v>
+      </c>
+      <c r="F48">
+        <v>143.06</v>
+      </c>
+      <c r="G48">
+        <v>4903</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Secretary</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>13516</v>
+      </c>
+      <c r="C49">
+        <v>2.48</v>
+      </c>
+      <c r="D49">
+        <v>4.97</v>
+      </c>
+      <c r="E49">
+        <v>0.5</v>
+      </c>
+      <c r="F49">
+        <v>64.73</v>
+      </c>
+      <c r="G49">
+        <v>3619</v>
+      </c>
+      <c r="H49">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Administrator</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>18603</v>
+      </c>
+      <c r="C50">
+        <v>3.83</v>
+      </c>
+      <c r="D50">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="E50">
+        <v>0.5</v>
+      </c>
+      <c r="F50">
+        <v>274.19</v>
+      </c>
+      <c r="G50">
+        <v>3355</v>
+      </c>
+      <c r="H50">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Manager</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>3954</v>
+      </c>
+      <c r="C51">
+        <v>2.84</v>
+      </c>
+      <c r="D51">
+        <v>6.1</v>
+      </c>
+      <c r="E51">
+        <v>0.5</v>
+      </c>
+      <c r="F51">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="G51">
+        <v>942</v>
+      </c>
+      <c r="H51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Sessional GP</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>15321</v>
+      </c>
+      <c r="C52">
+        <v>3.03</v>
+      </c>
+      <c r="D52">
+        <v>6.29</v>
+      </c>
+      <c r="E52">
+        <v>0.5</v>
+      </c>
+      <c r="F52">
+        <v>76.05</v>
+      </c>
+      <c r="G52">
+        <v>3311</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Sister/Charge Nurse</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>2965</v>
+      </c>
+      <c r="C53">
+        <v>2.68</v>
+      </c>
+      <c r="D53">
+        <v>5.52</v>
+      </c>
+      <c r="E53">
+        <v>0.5</v>
+      </c>
+      <c r="F53">
+        <v>60.04</v>
+      </c>
+      <c r="G53">
+        <v>702</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Social Worker</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>9</v>
+      </c>
+      <c r="C54">
+        <v>4.53</v>
+      </c>
+      <c r="D54">
+        <v>2.94</v>
+      </c>
+      <c r="E54">
+        <v>1.65</v>
+      </c>
+      <c r="F54">
+        <v>5.81</v>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Specialist Nurse Practitioner</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>14765</v>
+      </c>
+      <c r="C55">
+        <v>2.83</v>
+      </c>
+      <c r="D55">
+        <v>5.62</v>
+      </c>
+      <c r="E55">
+        <v>0.5</v>
+      </c>
+      <c r="F55">
+        <v>102.63</v>
+      </c>
+      <c r="G55">
+        <v>3450</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>140</v>
+      </c>
+      <c r="C56">
+        <v>2.21</v>
+      </c>
+      <c r="D56">
+        <v>3.76</v>
+      </c>
+      <c r="E56">
+        <v>0.5</v>
+      </c>
+      <c r="F56">
+        <v>19.74</v>
+      </c>
+      <c r="G56">
+        <v>41</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Staff Nurse</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>8286</v>
+      </c>
+      <c r="C57">
+        <v>2.9</v>
+      </c>
+      <c r="D57">
+        <v>6.99</v>
+      </c>
+      <c r="E57">
+        <v>0.5</v>
+      </c>
+      <c r="F57">
+        <v>154.22</v>
+      </c>
+      <c r="G57">
+        <v>1845</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>System Administrator</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>55535</v>
+      </c>
+      <c r="C58">
+        <v>7.07</v>
+      </c>
+      <c r="D58">
+        <v>11.92</v>
+      </c>
+      <c r="E58">
+        <v>0.5</v>
+      </c>
+      <c r="F58">
+        <v>135.66</v>
+      </c>
+      <c r="G58">
+        <v>5805</v>
+      </c>
+      <c r="H58">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>System Worker</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>1251</v>
+      </c>
+      <c r="C59">
+        <v>5.79</v>
+      </c>
+      <c r="D59">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="E59">
+        <v>0.5</v>
+      </c>
+      <c r="F59">
+        <v>66.41</v>
+      </c>
+      <c r="G59">
+        <v>152</v>
+      </c>
+      <c r="H59">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Therapist</t>
         </is>
       </c>
-      <c r="B34">
+      <c r="B60">
         <v>51</v>
       </c>
-      <c r="C34">
+      <c r="C60">
         <v>3.38</v>
       </c>
-      <c r="D34">
+      <c r="D60">
         <v>5.11</v>
       </c>
-      <c r="E34">
-        <v>0.5</v>
-      </c>
-      <c r="F34">
+      <c r="E60">
+        <v>0.5</v>
+      </c>
+      <c r="F60">
         <v>19.48</v>
       </c>
-      <c r="G34">
+      <c r="G60">
         <v>13</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2120,22 +3152,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>404780</v>
+        <v>473745</v>
       </c>
       <c r="C2">
-        <v>13.69</v>
+        <v>16.07</v>
       </c>
       <c r="D2">
-        <v>14.72</v>
+        <v>19.44</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>229.48</v>
+        <v>263.62</v>
       </c>
       <c r="G2">
-        <v>22167</v>
+        <v>22067</v>
       </c>
     </row>
     <row r="3">
@@ -2145,22 +3177,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>40711</v>
+        <v>101524</v>
       </c>
       <c r="C3">
-        <v>2.98</v>
+        <v>4.29</v>
       </c>
       <c r="D3">
-        <v>6.07</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>162.05</v>
+        <v>226.35</v>
       </c>
       <c r="G3">
-        <v>9078</v>
+        <v>15734</v>
       </c>
     </row>
     <row r="4">
@@ -2170,22 +3202,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>42958</v>
+        <v>94918</v>
       </c>
       <c r="C4">
-        <v>4.74</v>
+        <v>4.78</v>
       </c>
       <c r="D4">
-        <v>9.15</v>
+        <v>10.44</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>112.76</v>
+        <v>217.35</v>
       </c>
       <c r="G4">
-        <v>6181</v>
+        <v>13580</v>
       </c>
     </row>
   </sheetData>
@@ -2195,7 +3227,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2234,55 +3266,66 @@
           <t>num_subjects_visited</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>num_non_users</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Administrative Non-clinical</t>
         </is>
       </c>
       <c r="B2">
-        <v>404780</v>
+        <v>413255</v>
       </c>
       <c r="C2">
-        <v>13.69</v>
+        <v>14.13</v>
       </c>
       <c r="D2">
-        <v>14.72</v>
+        <v>21.64</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>229.48</v>
+        <v>796.1900000000001</v>
       </c>
       <c r="G2">
-        <v>22167</v>
+        <v>22096</v>
+      </c>
+      <c r="H2">
+        <v>545</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Not Clinically Relevant</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>473745</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>16.07</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>19.44</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>263.62</v>
       </c>
       <c r="G3">
-        <v>699</v>
+        <v>22067</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -2292,22 +3335,25 @@
         </is>
       </c>
       <c r="B4">
-        <v>40711</v>
+        <v>101524</v>
       </c>
       <c r="C4">
-        <v>2.98</v>
+        <v>4.29</v>
       </c>
       <c r="D4">
-        <v>6.07</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>162.05</v>
+        <v>226.35</v>
       </c>
       <c r="G4">
-        <v>9078</v>
+        <v>15734</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2317,22 +3363,25 @@
         </is>
       </c>
       <c r="B5">
-        <v>42958</v>
+        <v>94918</v>
       </c>
       <c r="C5">
-        <v>4.74</v>
+        <v>4.78</v>
       </c>
       <c r="D5">
-        <v>9.15</v>
+        <v>10.44</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>112.76</v>
+        <v>217.35</v>
       </c>
       <c r="G5">
-        <v>6181</v>
+        <v>13580</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/Output_visits_Raw.xlsx
@@ -354,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -401,19 +401,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>346</v>
+        <v>267</v>
       </c>
       <c r="C2">
-        <v>2.87</v>
+        <v>2.21</v>
       </c>
       <c r="D2">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>21.51</v>
+        <v>16.79</v>
       </c>
       <c r="G2">
         <v>81</v>
@@ -422,975 +422,800 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Assistant Practitioner</t>
+          <t>Associate Practitioner - General Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>581</v>
+        <v>2122</v>
       </c>
       <c r="C3">
-        <v>2.78</v>
+        <v>3.18</v>
       </c>
       <c r="D3">
-        <v>5.43</v>
+        <v>6.24</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>31.56</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G3">
-        <v>134</v>
+        <v>452</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Practitioner - General Practitioner</t>
+          <t>Associate Practitioner - Nurse</t>
         </is>
       </c>
       <c r="B4">
-        <v>2996</v>
+        <v>1950</v>
       </c>
       <c r="C4">
-        <v>4.49</v>
+        <v>2.02</v>
       </c>
       <c r="D4">
-        <v>10.74</v>
+        <v>4.19</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>150.86</v>
+        <v>44.54</v>
       </c>
       <c r="G4">
-        <v>452</v>
+        <v>627</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Practitioner - Nurse</t>
+          <t>Associate Specialist</t>
         </is>
       </c>
       <c r="B5">
-        <v>2457</v>
+        <v>192</v>
       </c>
       <c r="C5">
-        <v>2.54</v>
+        <v>2.12</v>
       </c>
       <c r="D5">
-        <v>5.57</v>
+        <v>5.27</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>56.82</v>
+        <v>34.6</v>
       </c>
       <c r="G5">
-        <v>627</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Specialist</t>
+          <t>Chiropodist/Podiatrist</t>
         </is>
       </c>
       <c r="B6">
-        <v>204</v>
+        <v>111</v>
       </c>
       <c r="C6">
-        <v>2.25</v>
+        <v>1.08</v>
       </c>
       <c r="D6">
-        <v>5.76</v>
+        <v>1.17</v>
       </c>
       <c r="E6">
         <v>0.5</v>
       </c>
       <c r="F6">
-        <v>38.45</v>
+        <v>5.5</v>
       </c>
       <c r="G6">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist</t>
+          <t>Clinical Psychologist</t>
         </is>
       </c>
       <c r="B7">
-        <v>119</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>1.16</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1.18</v>
+        <v>0.71</v>
       </c>
       <c r="E7">
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>60</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Clinical Assistant</t>
+          <t>Community Mental Health Nurse</t>
         </is>
       </c>
       <c r="B8">
-        <v>580</v>
+        <v>90</v>
       </c>
       <c r="C8">
-        <v>2.57</v>
+        <v>2.22</v>
       </c>
       <c r="D8">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>25.48</v>
+        <v>14.05</v>
       </c>
       <c r="G8">
-        <v>146</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Clinical Psychologist</t>
+          <t>Community Nurse</t>
         </is>
       </c>
       <c r="B9">
-        <v>8</v>
+        <v>15343</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>2.69</v>
       </c>
       <c r="D9">
-        <v>0.71</v>
+        <v>5.93</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>2</v>
+        <v>162.05</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>3742</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Community Mental Health Nurse</t>
+          <t>Community Practitioner</t>
         </is>
       </c>
       <c r="B10">
-        <v>93</v>
+        <v>43287</v>
       </c>
       <c r="C10">
-        <v>2.29</v>
+        <v>2.94</v>
       </c>
       <c r="D10">
-        <v>3.9</v>
+        <v>5.46</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>14.05</v>
+        <v>186.45</v>
       </c>
       <c r="G10">
-        <v>29</v>
+        <v>9496</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Community Nurse</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B11">
-        <v>18702</v>
+        <v>2046</v>
       </c>
       <c r="C11">
-        <v>3.27</v>
+        <v>2.87</v>
       </c>
       <c r="D11">
-        <v>7.98</v>
+        <v>5.91</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>182.62</v>
+        <v>45.66</v>
       </c>
       <c r="G11">
-        <v>3742</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Community Practitioner</t>
+          <t>Counsellor</t>
         </is>
       </c>
       <c r="B12">
-        <v>49421</v>
+        <v>128</v>
       </c>
       <c r="C12">
-        <v>3.36</v>
+        <v>2.66</v>
       </c>
       <c r="D12">
-        <v>6.63</v>
+        <v>3.21</v>
       </c>
       <c r="E12">
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>197.92</v>
+        <v>15.01</v>
       </c>
       <c r="G12">
-        <v>9496</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Dietitian</t>
         </is>
       </c>
       <c r="B13">
-        <v>2232</v>
+        <v>79</v>
       </c>
       <c r="C13">
-        <v>3.13</v>
+        <v>0.87</v>
       </c>
       <c r="D13">
-        <v>6.95</v>
+        <v>1.46</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>54.4</v>
+        <v>8.82</v>
       </c>
       <c r="G13">
-        <v>465</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Counsellor</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="B14">
-        <v>152</v>
+        <v>11921</v>
       </c>
       <c r="C14">
-        <v>3.16</v>
+        <v>1.85</v>
       </c>
       <c r="D14">
-        <v>4.2</v>
+        <v>3.76</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>19.51</v>
+        <v>71.27</v>
       </c>
       <c r="G14">
-        <v>28</v>
+        <v>4204</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dietitian</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="B15">
-        <v>81</v>
+        <v>303981</v>
       </c>
       <c r="C15">
-        <v>0.89</v>
+        <v>10.5</v>
       </c>
       <c r="D15">
-        <v>1.74</v>
+        <v>12.21</v>
       </c>
       <c r="E15">
         <v>0.5</v>
       </c>
       <c r="F15">
-        <v>8.91</v>
+        <v>166.11</v>
       </c>
       <c r="G15">
-        <v>55</v>
+        <v>21488</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="B16">
-        <v>14349</v>
+        <v>37858</v>
       </c>
       <c r="C16">
-        <v>2.23</v>
+        <v>5.14</v>
       </c>
       <c r="D16">
-        <v>5.12</v>
+        <v>9.69</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>115.81</v>
+        <v>112.76</v>
       </c>
       <c r="G16">
-        <v>4204</v>
+        <v>5023</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="B17">
-        <v>401172</v>
+        <v>4765</v>
       </c>
       <c r="C17">
-        <v>13.85</v>
+        <v>2.43</v>
       </c>
       <c r="D17">
-        <v>17.77</v>
+        <v>5.19</v>
       </c>
       <c r="E17">
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>249.91</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="G17">
-        <v>21488</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="B18">
-        <v>46310</v>
+        <v>837</v>
       </c>
       <c r="C18">
-        <v>6.28</v>
+        <v>2.11</v>
       </c>
       <c r="D18">
-        <v>13.84</v>
+        <v>3.57</v>
       </c>
       <c r="E18">
         <v>0.5</v>
       </c>
       <c r="F18">
-        <v>197.74</v>
+        <v>23.56</v>
       </c>
       <c r="G18">
-        <v>5023</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Healthcare Assistant</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B19">
-        <v>29189</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>2.59</v>
+        <v>0.5</v>
       </c>
       <c r="D19">
-        <v>4.61</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>84.52</v>
+        <v>0.5</v>
       </c>
       <c r="G19">
-        <v>7339</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="B20">
-        <v>6025</v>
+        <v>212</v>
       </c>
       <c r="C20">
-        <v>3.08</v>
+        <v>3.64</v>
       </c>
       <c r="D20">
-        <v>7.96</v>
+        <v>6.36</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>165.23</v>
+        <v>32.23</v>
       </c>
       <c r="G20">
-        <v>1302</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B21">
-        <v>873</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>23.56</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>263</v>
+        <v>21921</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>1580</v>
       </c>
       <c r="C22">
-        <v>0.5</v>
+        <v>2.14</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>0.5</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G22">
-        <v>3</v>
+        <v>468</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Modern Matron</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="B23">
-        <v>224</v>
+        <v>334</v>
       </c>
       <c r="C23">
-        <v>3.85</v>
+        <v>1.94</v>
       </c>
       <c r="D23">
-        <v>6.71</v>
+        <v>3.45</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>32.23</v>
+        <v>23.05</v>
       </c>
       <c r="G23">
-        <v>42</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Nurse Consultant</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B24">
-        <v>1916</v>
+        <v>211</v>
       </c>
       <c r="C24">
-        <v>2.6</v>
+        <v>1.37</v>
       </c>
       <c r="D24">
-        <v>6.41</v>
+        <v>3.27</v>
       </c>
       <c r="E24">
         <v>0.5</v>
       </c>
       <c r="F24">
-        <v>77.04000000000001</v>
+        <v>22.14</v>
       </c>
       <c r="G24">
-        <v>468</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Nurse Manager</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="B25">
-        <v>2695</v>
+        <v>217</v>
       </c>
       <c r="C25">
-        <v>2.77</v>
+        <v>1.55</v>
       </c>
       <c r="D25">
-        <v>6.68</v>
+        <v>2.52</v>
       </c>
       <c r="E25">
         <v>0.5</v>
       </c>
       <c r="F25">
-        <v>84.94</v>
+        <v>12.95</v>
       </c>
       <c r="G25">
-        <v>616</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Other Community Health Service</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="B26">
-        <v>357</v>
+        <v>474</v>
       </c>
       <c r="C26">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="D26">
-        <v>3.61</v>
+        <v>2.81</v>
       </c>
       <c r="E26">
         <v>0.5</v>
       </c>
       <c r="F26">
-        <v>24.82</v>
+        <v>23.95</v>
       </c>
       <c r="G26">
-        <v>121</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Salaried General Practitioner</t>
         </is>
       </c>
       <c r="B27">
-        <v>255</v>
+        <v>26363</v>
       </c>
       <c r="C27">
-        <v>1.66</v>
+        <v>3.74</v>
       </c>
       <c r="D27">
-        <v>4.07</v>
+        <v>6.71</v>
       </c>
       <c r="E27">
         <v>0.5</v>
       </c>
       <c r="F27">
-        <v>22.14</v>
+        <v>81.17</v>
       </c>
       <c r="G27">
-        <v>116</v>
+        <v>4903</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Paramedic Specialist Practitioner</t>
+          <t>Sessional GP</t>
         </is>
       </c>
       <c r="B28">
-        <v>271</v>
+        <v>12341</v>
       </c>
       <c r="C28">
-        <v>1.94</v>
+        <v>2.44</v>
       </c>
       <c r="D28">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="E28">
         <v>0.5</v>
       </c>
       <c r="F28">
-        <v>44.04</v>
+        <v>53.89</v>
       </c>
       <c r="G28">
-        <v>110</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Sister/Charge Nurse</t>
         </is>
       </c>
       <c r="B29">
-        <v>6001</v>
+        <v>2480</v>
       </c>
       <c r="C29">
-        <v>1.72</v>
+        <v>2.24</v>
       </c>
       <c r="D29">
-        <v>3.44</v>
+        <v>4.62</v>
       </c>
       <c r="E29">
         <v>0.5</v>
       </c>
       <c r="F29">
-        <v>36.89</v>
+        <v>52.54</v>
       </c>
       <c r="G29">
-        <v>2412</v>
+        <v>702</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Phlebotomist</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B30">
-        <v>6611</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>2.27</v>
+        <v>3.53</v>
       </c>
       <c r="D30">
-        <v>3.98</v>
+        <v>1.92</v>
       </c>
       <c r="E30">
-        <v>0.5</v>
+        <v>1.65</v>
       </c>
       <c r="F30">
-        <v>48.63</v>
+        <v>4.36</v>
       </c>
       <c r="G30">
-        <v>1865</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Specialist Nurse Practitioner</t>
         </is>
       </c>
       <c r="B31">
-        <v>22</v>
+        <v>11985</v>
       </c>
       <c r="C31">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="D31">
-        <v>1.37</v>
+        <v>4.29</v>
       </c>
       <c r="E31">
         <v>0.5</v>
       </c>
       <c r="F31">
-        <v>4.5</v>
+        <v>59.63</v>
       </c>
       <c r="G31">
-        <v>9</v>
+        <v>3450</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Physiotherapist</t>
+          <t>Specialist Practitioner</t>
         </is>
       </c>
       <c r="B32">
-        <v>493</v>
+        <v>135</v>
       </c>
       <c r="C32">
-        <v>1.78</v>
+        <v>2.13</v>
       </c>
       <c r="D32">
-        <v>2.85</v>
+        <v>3.78</v>
       </c>
       <c r="E32">
         <v>0.5</v>
       </c>
       <c r="F32">
-        <v>23.95</v>
+        <v>19.74</v>
       </c>
       <c r="G32">
-        <v>178</v>
+        <v>41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Radiographer</t>
+          <t>Staff Nurse</t>
         </is>
       </c>
       <c r="B33">
-        <v>30</v>
+        <v>7071</v>
       </c>
       <c r="C33">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="D33">
-        <v>1.71</v>
+        <v>5.83</v>
       </c>
       <c r="E33">
         <v>0.5</v>
       </c>
       <c r="F33">
-        <v>5.5</v>
+        <v>146.1</v>
       </c>
       <c r="G33">
-        <v>7</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Salaried General Practitioner</t>
+          <t>Therapist</t>
         </is>
       </c>
       <c r="B34">
-        <v>33882</v>
+        <v>51</v>
       </c>
       <c r="C34">
-        <v>4.81</v>
+        <v>3.38</v>
       </c>
       <c r="D34">
-        <v>9.529999999999999</v>
+        <v>5.11</v>
       </c>
       <c r="E34">
         <v>0.5</v>
       </c>
       <c r="F34">
-        <v>143.06</v>
+        <v>19.48</v>
       </c>
       <c r="G34">
-        <v>4903</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Sessional GP</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>15321</v>
-      </c>
-      <c r="C35">
-        <v>3.03</v>
-      </c>
-      <c r="D35">
-        <v>6.29</v>
-      </c>
-      <c r="E35">
-        <v>0.5</v>
-      </c>
-      <c r="F35">
-        <v>76.05</v>
-      </c>
-      <c r="G35">
-        <v>3311</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Sister/Charge Nurse</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>2965</v>
-      </c>
-      <c r="C36">
-        <v>2.68</v>
-      </c>
-      <c r="D36">
-        <v>5.52</v>
-      </c>
-      <c r="E36">
-        <v>0.5</v>
-      </c>
-      <c r="F36">
-        <v>60.04</v>
-      </c>
-      <c r="G36">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Social Worker</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>9</v>
-      </c>
-      <c r="C37">
-        <v>4.53</v>
-      </c>
-      <c r="D37">
-        <v>2.94</v>
-      </c>
-      <c r="E37">
-        <v>1.65</v>
-      </c>
-      <c r="F37">
-        <v>5.81</v>
-      </c>
-      <c r="G37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Specialist Nurse Practitioner</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>14765</v>
-      </c>
-      <c r="C38">
-        <v>2.83</v>
-      </c>
-      <c r="D38">
-        <v>5.62</v>
-      </c>
-      <c r="E38">
-        <v>0.5</v>
-      </c>
-      <c r="F38">
-        <v>102.63</v>
-      </c>
-      <c r="G38">
-        <v>3450</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>140</v>
-      </c>
-      <c r="C39">
-        <v>2.21</v>
-      </c>
-      <c r="D39">
-        <v>3.76</v>
-      </c>
-      <c r="E39">
-        <v>0.5</v>
-      </c>
-      <c r="F39">
-        <v>19.74</v>
-      </c>
-      <c r="G39">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Staff Nurse</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>8286</v>
-      </c>
-      <c r="C40">
-        <v>2.9</v>
-      </c>
-      <c r="D40">
-        <v>6.99</v>
-      </c>
-      <c r="E40">
-        <v>0.5</v>
-      </c>
-      <c r="F40">
-        <v>154.22</v>
-      </c>
-      <c r="G40">
-        <v>1845</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Therapist</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>51</v>
-      </c>
-      <c r="C41">
-        <v>3.38</v>
-      </c>
-      <c r="D41">
-        <v>5.11</v>
-      </c>
-      <c r="E41">
-        <v>0.5</v>
-      </c>
-      <c r="F41">
-        <v>19.48</v>
-      </c>
-      <c r="G41">
         <v>13</v>
       </c>
     </row>
@@ -1401,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1453,19 +1278,19 @@
         </is>
       </c>
       <c r="B2">
-        <v>346</v>
+        <v>267</v>
       </c>
       <c r="C2">
-        <v>2.87</v>
+        <v>2.21</v>
       </c>
       <c r="D2">
-        <v>4.1</v>
+        <v>3.15</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>21.51</v>
+        <v>16.79</v>
       </c>
       <c r="G2">
         <v>81</v>
@@ -1477,26 +1302,26 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Associate Practitioner - General Practitioner</t>
         </is>
       </c>
       <c r="B3">
-        <v>79</v>
+        <v>2122</v>
       </c>
       <c r="C3">
-        <v>1.42</v>
+        <v>3.18</v>
       </c>
       <c r="D3">
-        <v>9.65</v>
+        <v>6.24</v>
       </c>
       <c r="E3">
         <v>0.5</v>
       </c>
       <c r="F3">
-        <v>57.07</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="G3">
-        <v>35</v>
+        <v>452</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1505,26 +1330,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Assistant Practitioner</t>
+          <t>Associate Practitioner - Nurse</t>
         </is>
       </c>
       <c r="B4">
-        <v>581</v>
+        <v>1950</v>
       </c>
       <c r="C4">
-        <v>2.78</v>
+        <v>2.02</v>
       </c>
       <c r="D4">
-        <v>5.43</v>
+        <v>4.19</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>31.56</v>
+        <v>44.54</v>
       </c>
       <c r="G4">
-        <v>134</v>
+        <v>627</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1533,26 +1358,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Practitioner - General Practitioner</t>
+          <t>Associate Specialist</t>
         </is>
       </c>
       <c r="B5">
-        <v>2996</v>
+        <v>192</v>
       </c>
       <c r="C5">
-        <v>4.49</v>
+        <v>2.12</v>
       </c>
       <c r="D5">
-        <v>10.74</v>
+        <v>5.27</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>150.86</v>
+        <v>34.6</v>
       </c>
       <c r="G5">
-        <v>452</v>
+        <v>62</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1561,26 +1386,26 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Associate Practitioner - Nurse</t>
+          <t>Chiropodist/Podiatrist</t>
         </is>
       </c>
       <c r="B6">
-        <v>2457</v>
+        <v>111</v>
       </c>
       <c r="C6">
-        <v>2.54</v>
+        <v>1.08</v>
       </c>
       <c r="D6">
-        <v>5.57</v>
+        <v>1.17</v>
       </c>
       <c r="E6">
         <v>0.5</v>
       </c>
       <c r="F6">
-        <v>56.82</v>
+        <v>5.5</v>
       </c>
       <c r="G6">
-        <v>627</v>
+        <v>60</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1589,26 +1414,26 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate Specialist</t>
+          <t>Clinical Psychologist</t>
         </is>
       </c>
       <c r="B7">
-        <v>204</v>
+        <v>8</v>
       </c>
       <c r="C7">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>5.76</v>
+        <v>0.71</v>
       </c>
       <c r="E7">
         <v>0.5</v>
       </c>
       <c r="F7">
-        <v>38.45</v>
+        <v>2</v>
       </c>
       <c r="G7">
-        <v>62</v>
+        <v>4</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -1617,26 +1442,26 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist</t>
+          <t>Community Mental Health Nurse</t>
         </is>
       </c>
       <c r="B8">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="C8">
-        <v>1.16</v>
+        <v>2.22</v>
       </c>
       <c r="D8">
-        <v>1.18</v>
+        <v>3.9</v>
       </c>
       <c r="E8">
         <v>0.5</v>
       </c>
       <c r="F8">
-        <v>5.5</v>
+        <v>14.05</v>
       </c>
       <c r="G8">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -1645,54 +1470,54 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Clerical Worker</t>
+          <t>Community Nurse</t>
         </is>
       </c>
       <c r="B9">
-        <v>52837</v>
+        <v>15343</v>
       </c>
       <c r="C9">
-        <v>4.56</v>
+        <v>2.69</v>
       </c>
       <c r="D9">
-        <v>10.58</v>
+        <v>5.93</v>
       </c>
       <c r="E9">
         <v>0.5</v>
       </c>
       <c r="F9">
-        <v>326.8</v>
+        <v>162.05</v>
       </c>
       <c r="G9">
-        <v>8053</v>
+        <v>3742</v>
       </c>
       <c r="H9">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Clinical Assistant</t>
+          <t>Community Practitioner</t>
         </is>
       </c>
       <c r="B10">
-        <v>580</v>
+        <v>43287</v>
       </c>
       <c r="C10">
-        <v>2.57</v>
+        <v>2.94</v>
       </c>
       <c r="D10">
-        <v>3.92</v>
+        <v>5.46</v>
       </c>
       <c r="E10">
         <v>0.5</v>
       </c>
       <c r="F10">
-        <v>25.48</v>
+        <v>186.45</v>
       </c>
       <c r="G10">
-        <v>146</v>
+        <v>9496</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1701,54 +1526,54 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Clinical Coder</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B11">
-        <v>4416</v>
+        <v>2046</v>
       </c>
       <c r="C11">
-        <v>3.46</v>
+        <v>2.87</v>
       </c>
       <c r="D11">
-        <v>7.57</v>
+        <v>5.91</v>
       </c>
       <c r="E11">
         <v>0.5</v>
       </c>
       <c r="F11">
-        <v>77.26000000000001</v>
+        <v>45.66</v>
       </c>
       <c r="G11">
-        <v>911</v>
+        <v>465</v>
       </c>
       <c r="H11">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Clinical Psychologist</t>
+          <t>Counsellor</t>
         </is>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>2.66</v>
       </c>
       <c r="D12">
-        <v>0.71</v>
+        <v>3.21</v>
       </c>
       <c r="E12">
         <v>0.5</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>15.01</v>
       </c>
       <c r="G12">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -1757,54 +1582,54 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Community Administrator</t>
+          <t>Dietitian</t>
         </is>
       </c>
       <c r="B13">
-        <v>25691</v>
+        <v>79</v>
       </c>
       <c r="C13">
-        <v>6.17</v>
+        <v>0.87</v>
       </c>
       <c r="D13">
-        <v>18.26</v>
+        <v>1.46</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13">
-        <v>738.38</v>
+        <v>8.82</v>
       </c>
       <c r="G13">
-        <v>2828</v>
+        <v>55</v>
       </c>
       <c r="H13">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Community Mental Health Nurse</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="B14">
-        <v>93</v>
+        <v>11921</v>
       </c>
       <c r="C14">
-        <v>2.29</v>
+        <v>1.85</v>
       </c>
       <c r="D14">
-        <v>3.9</v>
+        <v>3.76</v>
       </c>
       <c r="E14">
         <v>0.5</v>
       </c>
       <c r="F14">
-        <v>14.05</v>
+        <v>71.27</v>
       </c>
       <c r="G14">
-        <v>29</v>
+        <v>4204</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1813,26 +1638,26 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Community Nurse</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="B15">
-        <v>18702</v>
+        <v>303981</v>
       </c>
       <c r="C15">
-        <v>3.27</v>
+        <v>10.5</v>
       </c>
       <c r="D15">
-        <v>7.98</v>
+        <v>12.21</v>
       </c>
       <c r="E15">
         <v>0.5</v>
       </c>
       <c r="F15">
-        <v>182.62</v>
+        <v>166.11</v>
       </c>
       <c r="G15">
-        <v>3742</v>
+        <v>21488</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -1841,26 +1666,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Community Practitioner</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="B16">
-        <v>49421</v>
+        <v>37858</v>
       </c>
       <c r="C16">
-        <v>3.36</v>
+        <v>5.14</v>
       </c>
       <c r="D16">
-        <v>6.63</v>
+        <v>9.69</v>
       </c>
       <c r="E16">
         <v>0.5</v>
       </c>
       <c r="F16">
-        <v>197.92</v>
+        <v>112.76</v>
       </c>
       <c r="G16">
-        <v>9496</v>
+        <v>5023</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1869,26 +1694,26 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="B17">
-        <v>2232</v>
+        <v>4765</v>
       </c>
       <c r="C17">
-        <v>3.13</v>
+        <v>2.43</v>
       </c>
       <c r="D17">
-        <v>6.95</v>
+        <v>5.19</v>
       </c>
       <c r="E17">
         <v>0.5</v>
       </c>
       <c r="F17">
-        <v>54.4</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="G17">
-        <v>465</v>
+        <v>1302</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -1897,26 +1722,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Counsellor</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="B18">
-        <v>152</v>
+        <v>837</v>
       </c>
       <c r="C18">
-        <v>3.16</v>
+        <v>2.11</v>
       </c>
       <c r="D18">
-        <v>4.2</v>
+        <v>3.57</v>
       </c>
       <c r="E18">
         <v>0.5</v>
       </c>
       <c r="F18">
-        <v>19.51</v>
+        <v>23.56</v>
       </c>
       <c r="G18">
-        <v>28</v>
+        <v>263</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -1925,138 +1750,138 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Desktop Support Administrator</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B19">
-        <v>24519</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>7.19</v>
+        <v>0.5</v>
       </c>
       <c r="D19">
-        <v>11.73</v>
+        <v>0</v>
       </c>
       <c r="E19">
         <v>0.5</v>
       </c>
       <c r="F19">
-        <v>97.40000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="G19">
-        <v>2486</v>
+        <v>3</v>
       </c>
       <c r="H19">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Desktop Support Technician</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="B20">
-        <v>1098</v>
+        <v>212</v>
       </c>
       <c r="C20">
-        <v>7.96</v>
+        <v>3.64</v>
       </c>
       <c r="D20">
-        <v>11.3</v>
+        <v>6.36</v>
       </c>
       <c r="E20">
         <v>0.5</v>
       </c>
       <c r="F20">
-        <v>52.18</v>
+        <v>32.23</v>
       </c>
       <c r="G20">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Dietitian</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B21">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0.89</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>8.91</v>
+        <v>0</v>
       </c>
       <c r="G21">
-        <v>55</v>
+        <v>22620</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>699</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Dispenser</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="B22">
-        <v>5766</v>
+        <v>1580</v>
       </c>
       <c r="C22">
-        <v>4.22</v>
+        <v>2.14</v>
       </c>
       <c r="D22">
-        <v>8.98</v>
+        <v>5.46</v>
       </c>
       <c r="E22">
         <v>0.5</v>
       </c>
       <c r="F22">
-        <v>133.63</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="G22">
-        <v>903</v>
+        <v>468</v>
       </c>
       <c r="H22">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="B23">
-        <v>14349</v>
+        <v>334</v>
       </c>
       <c r="C23">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="D23">
-        <v>5.12</v>
+        <v>3.45</v>
       </c>
       <c r="E23">
         <v>0.5</v>
       </c>
       <c r="F23">
-        <v>115.81</v>
+        <v>23.05</v>
       </c>
       <c r="G23">
-        <v>4204</v>
+        <v>121</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2065,26 +1890,26 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B24">
-        <v>401172</v>
+        <v>211</v>
       </c>
       <c r="C24">
-        <v>13.85</v>
+        <v>1.37</v>
       </c>
       <c r="D24">
-        <v>17.77</v>
+        <v>3.27</v>
       </c>
       <c r="E24">
         <v>0.5</v>
       </c>
       <c r="F24">
-        <v>249.91</v>
+        <v>22.14</v>
       </c>
       <c r="G24">
-        <v>21488</v>
+        <v>116</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -2093,26 +1918,26 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="B25">
-        <v>46310</v>
+        <v>217</v>
       </c>
       <c r="C25">
-        <v>6.28</v>
+        <v>1.55</v>
       </c>
       <c r="D25">
-        <v>13.84</v>
+        <v>2.52</v>
       </c>
       <c r="E25">
         <v>0.5</v>
       </c>
       <c r="F25">
-        <v>197.74</v>
+        <v>12.95</v>
       </c>
       <c r="G25">
-        <v>5023</v>
+        <v>110</v>
       </c>
       <c r="H25">
         <v>0</v>
@@ -2121,54 +1946,54 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Health Records Administrator</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="B26">
-        <v>541</v>
+        <v>474</v>
       </c>
       <c r="C26">
-        <v>1.98</v>
+        <v>1.71</v>
       </c>
       <c r="D26">
-        <v>3.73</v>
+        <v>2.81</v>
       </c>
       <c r="E26">
         <v>0.5</v>
       </c>
       <c r="F26">
-        <v>29.22</v>
+        <v>23.95</v>
       </c>
       <c r="G26">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H26">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Healthcare Assistant</t>
+          <t>Salaried General Practitioner</t>
         </is>
       </c>
       <c r="B27">
-        <v>29189</v>
+        <v>26363</v>
       </c>
       <c r="C27">
-        <v>2.59</v>
+        <v>3.74</v>
       </c>
       <c r="D27">
-        <v>4.61</v>
+        <v>6.71</v>
       </c>
       <c r="E27">
         <v>0.5</v>
       </c>
       <c r="F27">
-        <v>84.52</v>
+        <v>81.17</v>
       </c>
       <c r="G27">
-        <v>7339</v>
+        <v>4903</v>
       </c>
       <c r="H27">
         <v>0</v>
@@ -2177,54 +2002,54 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Helpdesk Administrator</t>
+          <t>Sessional GP</t>
         </is>
       </c>
       <c r="B28">
-        <v>1225</v>
+        <v>12341</v>
       </c>
       <c r="C28">
-        <v>5.14</v>
+        <v>2.44</v>
       </c>
       <c r="D28">
-        <v>13.52</v>
+        <v>4.75</v>
       </c>
       <c r="E28">
         <v>0.5</v>
       </c>
       <c r="F28">
-        <v>115.81</v>
+        <v>53.89</v>
       </c>
       <c r="G28">
-        <v>165</v>
+        <v>3311</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>Sister/Charge Nurse</t>
         </is>
       </c>
       <c r="B29">
-        <v>6025</v>
+        <v>2480</v>
       </c>
       <c r="C29">
-        <v>3.08</v>
+        <v>2.24</v>
       </c>
       <c r="D29">
-        <v>7.96</v>
+        <v>4.62</v>
       </c>
       <c r="E29">
         <v>0.5</v>
       </c>
       <c r="F29">
-        <v>165.23</v>
+        <v>52.54</v>
       </c>
       <c r="G29">
-        <v>1302</v>
+        <v>702</v>
       </c>
       <c r="H29">
         <v>0</v>
@@ -2233,868 +2058,140 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B30">
-        <v>85436</v>
+        <v>7</v>
       </c>
       <c r="C30">
-        <v>5.51</v>
+        <v>3.53</v>
       </c>
       <c r="D30">
-        <v>11.02</v>
+        <v>1.92</v>
       </c>
       <c r="E30">
-        <v>0.5</v>
+        <v>1.65</v>
       </c>
       <c r="F30">
-        <v>239.44</v>
+        <v>4.36</v>
       </c>
       <c r="G30">
-        <v>11066</v>
+        <v>2</v>
       </c>
       <c r="H30">
-        <v>212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Medical Records Clerk</t>
+          <t>Specialist Nurse Practitioner</t>
         </is>
       </c>
       <c r="B31">
-        <v>1011</v>
+        <v>11985</v>
       </c>
       <c r="C31">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="D31">
-        <v>7.31</v>
+        <v>4.29</v>
       </c>
       <c r="E31">
         <v>0.5</v>
       </c>
       <c r="F31">
-        <v>50.19</v>
+        <v>59.63</v>
       </c>
       <c r="G31">
-        <v>195</v>
+        <v>3450</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Medical Secretary</t>
+          <t>Specialist Practitioner</t>
         </is>
       </c>
       <c r="B32">
-        <v>15820</v>
+        <v>135</v>
       </c>
       <c r="C32">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="D32">
-        <v>6.57</v>
+        <v>3.78</v>
       </c>
       <c r="E32">
         <v>0.5</v>
       </c>
       <c r="F32">
-        <v>118.17</v>
+        <v>19.74</v>
       </c>
       <c r="G32">
-        <v>4259</v>
+        <v>41</v>
       </c>
       <c r="H32">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Medical Student</t>
+          <t>Staff Nurse</t>
         </is>
       </c>
       <c r="B33">
-        <v>236</v>
+        <v>7071</v>
       </c>
       <c r="C33">
-        <v>0.78</v>
+        <v>2.48</v>
       </c>
       <c r="D33">
-        <v>1.42</v>
+        <v>5.83</v>
       </c>
       <c r="E33">
         <v>0.5</v>
       </c>
       <c r="F33">
-        <v>11.41</v>
+        <v>146.1</v>
       </c>
       <c r="G33">
-        <v>193</v>
+        <v>1845</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Therapist</t>
         </is>
       </c>
       <c r="B34">
-        <v>873</v>
+        <v>51</v>
       </c>
       <c r="C34">
-        <v>2.2</v>
+        <v>3.38</v>
       </c>
       <c r="D34">
-        <v>3.78</v>
+        <v>5.11</v>
       </c>
       <c r="E34">
         <v>0.5</v>
       </c>
       <c r="F34">
-        <v>23.56</v>
+        <v>19.48</v>
       </c>
       <c r="G34">
-        <v>263</v>
+        <v>13</v>
       </c>
       <c r="H34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Midwife</t>
-        </is>
-      </c>
-      <c r="B35">
-        <v>3</v>
-      </c>
-      <c r="C35">
-        <v>0.5</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0.5</v>
-      </c>
-      <c r="F35">
-        <v>0.5</v>
-      </c>
-      <c r="G35">
-        <v>3</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Modern Matron</t>
-        </is>
-      </c>
-      <c r="B36">
-        <v>224</v>
-      </c>
-      <c r="C36">
-        <v>3.85</v>
-      </c>
-      <c r="D36">
-        <v>6.71</v>
-      </c>
-      <c r="E36">
-        <v>0.5</v>
-      </c>
-      <c r="F36">
-        <v>32.23</v>
-      </c>
-      <c r="G36">
-        <v>42</v>
-      </c>
-      <c r="H36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Nurse Consultant</t>
-        </is>
-      </c>
-      <c r="B37">
-        <v>1916</v>
-      </c>
-      <c r="C37">
-        <v>2.6</v>
-      </c>
-      <c r="D37">
-        <v>6.41</v>
-      </c>
-      <c r="E37">
-        <v>0.5</v>
-      </c>
-      <c r="F37">
-        <v>77.04000000000001</v>
-      </c>
-      <c r="G37">
-        <v>468</v>
-      </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Nurse Manager</t>
-        </is>
-      </c>
-      <c r="B38">
-        <v>2695</v>
-      </c>
-      <c r="C38">
-        <v>2.77</v>
-      </c>
-      <c r="D38">
-        <v>6.68</v>
-      </c>
-      <c r="E38">
-        <v>0.5</v>
-      </c>
-      <c r="F38">
-        <v>84.94</v>
-      </c>
-      <c r="G38">
-        <v>616</v>
-      </c>
-      <c r="H38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Other Community Health Service</t>
-        </is>
-      </c>
-      <c r="B39">
-        <v>357</v>
-      </c>
-      <c r="C39">
-        <v>2.08</v>
-      </c>
-      <c r="D39">
-        <v>3.61</v>
-      </c>
-      <c r="E39">
-        <v>0.5</v>
-      </c>
-      <c r="F39">
-        <v>24.82</v>
-      </c>
-      <c r="G39">
-        <v>121</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Paramedic</t>
-        </is>
-      </c>
-      <c r="B40">
-        <v>255</v>
-      </c>
-      <c r="C40">
-        <v>1.66</v>
-      </c>
-      <c r="D40">
-        <v>4.07</v>
-      </c>
-      <c r="E40">
-        <v>0.5</v>
-      </c>
-      <c r="F40">
-        <v>22.14</v>
-      </c>
-      <c r="G40">
-        <v>116</v>
-      </c>
-      <c r="H40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Paramedic Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B41">
-        <v>271</v>
-      </c>
-      <c r="C41">
-        <v>1.94</v>
-      </c>
-      <c r="D41">
-        <v>4.9</v>
-      </c>
-      <c r="E41">
-        <v>0.5</v>
-      </c>
-      <c r="F41">
-        <v>44.04</v>
-      </c>
-      <c r="G41">
-        <v>110</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Pharmacist</t>
-        </is>
-      </c>
-      <c r="B42">
-        <v>6001</v>
-      </c>
-      <c r="C42">
-        <v>1.72</v>
-      </c>
-      <c r="D42">
-        <v>3.44</v>
-      </c>
-      <c r="E42">
-        <v>0.5</v>
-      </c>
-      <c r="F42">
-        <v>36.89</v>
-      </c>
-      <c r="G42">
-        <v>2412</v>
-      </c>
-      <c r="H42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Phlebotomist</t>
-        </is>
-      </c>
-      <c r="B43">
-        <v>6611</v>
-      </c>
-      <c r="C43">
-        <v>2.27</v>
-      </c>
-      <c r="D43">
-        <v>3.98</v>
-      </c>
-      <c r="E43">
-        <v>0.5</v>
-      </c>
-      <c r="F43">
-        <v>48.63</v>
-      </c>
-      <c r="G43">
-        <v>1865</v>
-      </c>
-      <c r="H43">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Physician Assistant</t>
-        </is>
-      </c>
-      <c r="B44">
-        <v>22</v>
-      </c>
-      <c r="C44">
-        <v>1.4</v>
-      </c>
-      <c r="D44">
-        <v>1.37</v>
-      </c>
-      <c r="E44">
-        <v>0.5</v>
-      </c>
-      <c r="F44">
-        <v>4.5</v>
-      </c>
-      <c r="G44">
-        <v>9</v>
-      </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Physiotherapist</t>
-        </is>
-      </c>
-      <c r="B45">
-        <v>493</v>
-      </c>
-      <c r="C45">
-        <v>1.78</v>
-      </c>
-      <c r="D45">
-        <v>2.85</v>
-      </c>
-      <c r="E45">
-        <v>0.5</v>
-      </c>
-      <c r="F45">
-        <v>23.95</v>
-      </c>
-      <c r="G45">
-        <v>178</v>
-      </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Radiographer</t>
-        </is>
-      </c>
-      <c r="B46">
-        <v>30</v>
-      </c>
-      <c r="C46">
-        <v>2.43</v>
-      </c>
-      <c r="D46">
-        <v>1.71</v>
-      </c>
-      <c r="E46">
-        <v>0.5</v>
-      </c>
-      <c r="F46">
-        <v>5.5</v>
-      </c>
-      <c r="G46">
-        <v>7</v>
-      </c>
-      <c r="H46">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Receptionist</t>
-        </is>
-      </c>
-      <c r="B47">
-        <v>101721</v>
-      </c>
-      <c r="C47">
-        <v>6.07</v>
-      </c>
-      <c r="D47">
-        <v>12.54</v>
-      </c>
-      <c r="E47">
-        <v>0.5</v>
-      </c>
-      <c r="F47">
-        <v>426.29</v>
-      </c>
-      <c r="G47">
-        <v>11764</v>
-      </c>
-      <c r="H47">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Salaried General Practitioner</t>
-        </is>
-      </c>
-      <c r="B48">
-        <v>33882</v>
-      </c>
-      <c r="C48">
-        <v>4.81</v>
-      </c>
-      <c r="D48">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="E48">
-        <v>0.5</v>
-      </c>
-      <c r="F48">
-        <v>143.06</v>
-      </c>
-      <c r="G48">
-        <v>4903</v>
-      </c>
-      <c r="H48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Secretary</t>
-        </is>
-      </c>
-      <c r="B49">
-        <v>13516</v>
-      </c>
-      <c r="C49">
-        <v>2.48</v>
-      </c>
-      <c r="D49">
-        <v>4.97</v>
-      </c>
-      <c r="E49">
-        <v>0.5</v>
-      </c>
-      <c r="F49">
-        <v>64.73</v>
-      </c>
-      <c r="G49">
-        <v>3619</v>
-      </c>
-      <c r="H49">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Senior Administrator</t>
-        </is>
-      </c>
-      <c r="B50">
-        <v>18603</v>
-      </c>
-      <c r="C50">
-        <v>3.83</v>
-      </c>
-      <c r="D50">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="E50">
-        <v>0.5</v>
-      </c>
-      <c r="F50">
-        <v>274.19</v>
-      </c>
-      <c r="G50">
-        <v>3355</v>
-      </c>
-      <c r="H50">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Senior Manager</t>
-        </is>
-      </c>
-      <c r="B51">
-        <v>3954</v>
-      </c>
-      <c r="C51">
-        <v>2.84</v>
-      </c>
-      <c r="D51">
-        <v>6.1</v>
-      </c>
-      <c r="E51">
-        <v>0.5</v>
-      </c>
-      <c r="F51">
-        <v>97.98999999999999</v>
-      </c>
-      <c r="G51">
-        <v>942</v>
-      </c>
-      <c r="H51">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Sessional GP</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>15321</v>
-      </c>
-      <c r="C52">
-        <v>3.03</v>
-      </c>
-      <c r="D52">
-        <v>6.29</v>
-      </c>
-      <c r="E52">
-        <v>0.5</v>
-      </c>
-      <c r="F52">
-        <v>76.05</v>
-      </c>
-      <c r="G52">
-        <v>3311</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Sister/Charge Nurse</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>2965</v>
-      </c>
-      <c r="C53">
-        <v>2.68</v>
-      </c>
-      <c r="D53">
-        <v>5.52</v>
-      </c>
-      <c r="E53">
-        <v>0.5</v>
-      </c>
-      <c r="F53">
-        <v>60.04</v>
-      </c>
-      <c r="G53">
-        <v>702</v>
-      </c>
-      <c r="H53">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Social Worker</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>9</v>
-      </c>
-      <c r="C54">
-        <v>4.53</v>
-      </c>
-      <c r="D54">
-        <v>2.94</v>
-      </c>
-      <c r="E54">
-        <v>1.65</v>
-      </c>
-      <c r="F54">
-        <v>5.81</v>
-      </c>
-      <c r="G54">
-        <v>2</v>
-      </c>
-      <c r="H54">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Specialist Nurse Practitioner</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>14765</v>
-      </c>
-      <c r="C55">
-        <v>2.83</v>
-      </c>
-      <c r="D55">
-        <v>5.62</v>
-      </c>
-      <c r="E55">
-        <v>0.5</v>
-      </c>
-      <c r="F55">
-        <v>102.63</v>
-      </c>
-      <c r="G55">
-        <v>3450</v>
-      </c>
-      <c r="H55">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Specialist Practitioner</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>140</v>
-      </c>
-      <c r="C56">
-        <v>2.21</v>
-      </c>
-      <c r="D56">
-        <v>3.76</v>
-      </c>
-      <c r="E56">
-        <v>0.5</v>
-      </c>
-      <c r="F56">
-        <v>19.74</v>
-      </c>
-      <c r="G56">
-        <v>41</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Staff Nurse</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>8286</v>
-      </c>
-      <c r="C57">
-        <v>2.9</v>
-      </c>
-      <c r="D57">
-        <v>6.99</v>
-      </c>
-      <c r="E57">
-        <v>0.5</v>
-      </c>
-      <c r="F57">
-        <v>154.22</v>
-      </c>
-      <c r="G57">
-        <v>1845</v>
-      </c>
-      <c r="H57">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>System Administrator</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>55535</v>
-      </c>
-      <c r="C58">
-        <v>7.07</v>
-      </c>
-      <c r="D58">
-        <v>11.92</v>
-      </c>
-      <c r="E58">
-        <v>0.5</v>
-      </c>
-      <c r="F58">
-        <v>135.66</v>
-      </c>
-      <c r="G58">
-        <v>5805</v>
-      </c>
-      <c r="H58">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>System Worker</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>1251</v>
-      </c>
-      <c r="C59">
-        <v>5.79</v>
-      </c>
-      <c r="D59">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="E59">
-        <v>0.5</v>
-      </c>
-      <c r="F59">
-        <v>66.41</v>
-      </c>
-      <c r="G59">
-        <v>152</v>
-      </c>
-      <c r="H59">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Therapist</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>51</v>
-      </c>
-      <c r="C60">
-        <v>3.38</v>
-      </c>
-      <c r="D60">
-        <v>5.11</v>
-      </c>
-      <c r="E60">
-        <v>0.5</v>
-      </c>
-      <c r="F60">
-        <v>19.48</v>
-      </c>
-      <c r="G60">
-        <v>13</v>
-      </c>
-      <c r="H60">
         <v>0</v>
       </c>
     </row>
@@ -3105,7 +2202,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -3152,72 +2249,97 @@
         </is>
       </c>
       <c r="B2">
-        <v>473745</v>
+        <v>404780</v>
       </c>
       <c r="C2">
-        <v>16.07</v>
+        <v>13.69</v>
       </c>
       <c r="D2">
-        <v>19.44</v>
+        <v>14.72</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>263.62</v>
+        <v>229.48</v>
       </c>
       <c r="G2">
-        <v>22067</v>
+        <v>22167</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B3">
-        <v>101524</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>8.470000000000001</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>226.35</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>15734</v>
+        <v>21921</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Nurse</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>40711</v>
+      </c>
+      <c r="C4">
+        <v>2.98</v>
+      </c>
+      <c r="D4">
+        <v>6.07</v>
+      </c>
+      <c r="E4">
+        <v>0.5</v>
+      </c>
+      <c r="F4">
+        <v>162.05</v>
+      </c>
+      <c r="G4">
+        <v>9078</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="B4">
-        <v>94918</v>
-      </c>
-      <c r="C4">
-        <v>4.78</v>
-      </c>
-      <c r="D4">
-        <v>10.44</v>
-      </c>
-      <c r="E4">
-        <v>0.5</v>
-      </c>
-      <c r="F4">
-        <v>217.35</v>
-      </c>
-      <c r="G4">
-        <v>13580</v>
+      <c r="B5">
+        <v>42958</v>
+      </c>
+      <c r="C5">
+        <v>4.74</v>
+      </c>
+      <c r="D5">
+        <v>9.15</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5">
+        <v>112.76</v>
+      </c>
+      <c r="G5">
+        <v>6181</v>
       </c>
     </row>
   </sheetData>
@@ -3275,57 +2397,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>General Practitioner</t>
         </is>
       </c>
       <c r="B2">
-        <v>413255</v>
+        <v>404780</v>
       </c>
       <c r="C2">
-        <v>14.13</v>
+        <v>13.69</v>
       </c>
       <c r="D2">
-        <v>21.64</v>
+        <v>14.72</v>
       </c>
       <c r="E2">
         <v>0.5</v>
       </c>
       <c r="F2">
-        <v>796.1900000000001</v>
+        <v>229.48</v>
       </c>
       <c r="G2">
-        <v>22096</v>
+        <v>22167</v>
       </c>
       <c r="H2">
-        <v>545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>Not Clinically Relevant</t>
         </is>
       </c>
       <c r="B3">
-        <v>473745</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>16.07</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>19.44</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>263.62</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>22067</v>
+        <v>22620</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>699</v>
       </c>
     </row>
     <row r="4">
@@ -3335,22 +2457,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>101524</v>
+        <v>40711</v>
       </c>
       <c r="C4">
-        <v>4.29</v>
+        <v>2.98</v>
       </c>
       <c r="D4">
-        <v>8.470000000000001</v>
+        <v>6.07</v>
       </c>
       <c r="E4">
         <v>0.5</v>
       </c>
       <c r="F4">
-        <v>226.35</v>
+        <v>162.05</v>
       </c>
       <c r="G4">
-        <v>15734</v>
+        <v>9078</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -3363,22 +2485,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>94918</v>
+        <v>42958</v>
       </c>
       <c r="C5">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="D5">
-        <v>10.44</v>
+        <v>9.15</v>
       </c>
       <c r="E5">
         <v>0.5</v>
       </c>
       <c r="F5">
-        <v>217.35</v>
+        <v>112.76</v>
       </c>
       <c r="G5">
-        <v>13580</v>
+        <v>6181</v>
       </c>
       <c r="H5">
         <v>0</v>
